--- a/預測結果與評估指標_kfold_mask幾何_年齡.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_年齡.xlsx
@@ -427,7 +427,7 @@
     <col min="3" max="3" width="13.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="14.7109375" customWidth="true"/>
+    <col min="6" max="6" width="15.42578125" customWidth="true"/>
     <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="17" customWidth="true"/>
     <col min="9" max="9" width="20.5703125" customWidth="true"/>
@@ -490,28 +490,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>403.60700000000003</v>
+        <v>405.481</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>20.937454380565207</v>
+        <v>21.003471696046692</v>
       </c>
       <c r="F2" s="0">
-        <v>-2.0625456194347933</v>
+        <v>-1.9965283039533084</v>
       </c>
       <c r="G2" s="0">
-        <v>2.0625456194347933</v>
+        <v>1.9965283039533084</v>
       </c>
       <c r="H2" s="0">
-        <v>20.437454380565207</v>
+        <v>20.503471696046692</v>
       </c>
       <c r="I2" s="0">
-        <v>-2.5625456194347933</v>
+        <v>-2.4965283039533084</v>
       </c>
       <c r="J2" s="0">
-        <v>2.5625456194347933</v>
+        <v>2.4965283039533084</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -534,28 +534,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.62289999999996</v>
+        <v>605.36530000000005</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>21.368702241906473</v>
+        <v>21.391752160002106</v>
       </c>
       <c r="F3" s="0">
-        <v>0.3687022419064725</v>
+        <v>0.39175216000210611</v>
       </c>
       <c r="G3" s="0">
-        <v>0.3687022419064725</v>
+        <v>0.39175216000210611</v>
       </c>
       <c r="H3" s="0">
-        <v>20.868702241906473</v>
+        <v>20.891752160002106</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.13129775809352751</v>
+        <v>-0.10824783999789389</v>
       </c>
       <c r="J3" s="0">
-        <v>0.13129775809352751</v>
+        <v>0.10824783999789389</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -578,28 +578,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>773.59109999999998</v>
+        <v>740.86210000000005</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>21.00338895416904</v>
+        <v>21.024082766863774</v>
       </c>
       <c r="F4" s="0">
-        <v>-2.4966110458309601</v>
+        <v>-2.4759172331362258</v>
       </c>
       <c r="G4" s="0">
-        <v>2.4966110458309601</v>
+        <v>2.4759172331362258</v>
       </c>
       <c r="H4" s="0">
-        <v>20.50338895416904</v>
+        <v>20.524082766863774</v>
       </c>
       <c r="I4" s="0">
-        <v>-2.9966110458309601</v>
+        <v>-2.9759172331362258</v>
       </c>
       <c r="J4" s="0">
-        <v>2.9966110458309601</v>
+        <v>2.9759172331362258</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -622,28 +622,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.42529999999999</v>
+        <v>580.86249999999996</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>20.94638657220564</v>
+        <v>21.003634692687584</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.053613427794360291</v>
+        <v>0.0036346926875836516</v>
       </c>
       <c r="G5" s="0">
-        <v>0.053613427794360291</v>
+        <v>0.0036346926875836516</v>
       </c>
       <c r="H5" s="0">
-        <v>20.44638657220564</v>
+        <v>20.503634692687584</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.55361342779436029</v>
+        <v>-0.49636530731241635</v>
       </c>
       <c r="J5" s="0">
-        <v>0.55361342779436029</v>
+        <v>0.49636530731241635</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -666,28 +666,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>632.08730000000003</v>
+        <v>620.73389999999995</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.393526934059047</v>
+        <v>21.418053005341442</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.1064730659409534</v>
+        <v>-0.081946994658558481</v>
       </c>
       <c r="G6" s="0">
-        <v>0.1064730659409534</v>
+        <v>0.081946994658558481</v>
       </c>
       <c r="H6" s="0">
-        <v>20.893526934059047</v>
+        <v>20.918053005341442</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.6064730659409534</v>
+        <v>-0.58194699465855848</v>
       </c>
       <c r="J6" s="0">
-        <v>0.6064730659409534</v>
+        <v>0.58194699465855848</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -710,28 +710,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>720.98979999999995</v>
+        <v>711.67399999999998</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>20.935708438179358</v>
+        <v>21.003415319883146</v>
       </c>
       <c r="F7" s="0">
-        <v>-1.0642915618206423</v>
+        <v>-0.99658468011685386</v>
       </c>
       <c r="G7" s="0">
-        <v>1.0642915618206423</v>
+        <v>0.99658468011685386</v>
       </c>
       <c r="H7" s="0">
-        <v>20.435708438179358</v>
+        <v>20.503415319883146</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.5642915618206423</v>
+        <v>-1.4965846801168539</v>
       </c>
       <c r="J7" s="0">
-        <v>1.5642915618206423</v>
+        <v>1.4965846801168539</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -754,28 +754,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>758.05489999999998</v>
+        <v>757.66719999999998</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>21.153677777616899</v>
+        <v>21.175926585647883</v>
       </c>
       <c r="F8" s="0">
-        <v>-3.8463222223831011</v>
+        <v>-3.8240734143521173</v>
       </c>
       <c r="G8" s="0">
-        <v>3.8463222223831011</v>
+        <v>3.8240734143521173</v>
       </c>
       <c r="H8" s="0">
-        <v>20.653677777616899</v>
+        <v>20.675926585647883</v>
       </c>
       <c r="I8" s="0">
-        <v>-4.3463222223831011</v>
+        <v>-4.3240734143521173</v>
       </c>
       <c r="J8" s="0">
-        <v>4.3463222223831011</v>
+        <v>4.3240734143521173</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -798,28 +798,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>400.07780000000002</v>
+        <v>390.43310000000002</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>20.998194519750825</v>
+        <v>20.966493622312711</v>
       </c>
       <c r="F9" s="0">
-        <v>0.49819451975082529</v>
+        <v>0.46649362231271141</v>
       </c>
       <c r="G9" s="0">
-        <v>0.49819451975082529</v>
+        <v>0.46649362231271141</v>
       </c>
       <c r="H9" s="0">
-        <v>20.498194519750825</v>
+        <v>20.466493622312711</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.0018054802491747068</v>
+        <v>-0.033506377687288591</v>
       </c>
       <c r="J9" s="0">
-        <v>0.0018054802491747068</v>
+        <v>0.033506377687288591</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -842,28 +842,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>1283.9973</v>
+        <v>1263.4103</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.249929707541696</v>
+        <v>21.247105366409329</v>
       </c>
       <c r="F10" s="0">
-        <v>0.24992970754169619</v>
+        <v>0.24710536640932901</v>
       </c>
       <c r="G10" s="0">
-        <v>0.24992970754169619</v>
+        <v>0.24710536640932901</v>
       </c>
       <c r="H10" s="0">
-        <v>20.749929707541696</v>
+        <v>20.747105366409329</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.25007029245830381</v>
+        <v>-0.25289463359067099</v>
       </c>
       <c r="J10" s="0">
-        <v>0.25007029245830381</v>
+        <v>0.25289463359067099</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -886,28 +886,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>317.95030000000003</v>
+        <v>319.74869999999999</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>20.939870587234246</v>
+        <v>21.003525317817989</v>
       </c>
       <c r="F11" s="0">
-        <v>2.9398705872342461</v>
+        <v>3.0035253178179886</v>
       </c>
       <c r="G11" s="0">
-        <v>2.9398705872342461</v>
+        <v>3.0035253178179886</v>
       </c>
       <c r="H11" s="0">
-        <v>20.439870587234246</v>
+        <v>20.503525317817989</v>
       </c>
       <c r="I11" s="0">
-        <v>2.4398705872342461</v>
+        <v>2.5035253178179886</v>
       </c>
       <c r="J11" s="0">
-        <v>2.4398705872342461</v>
+        <v>2.5035253178179886</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -930,28 +930,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>750.11170000000004</v>
+        <v>718.36379999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>20.81108743760327</v>
+        <v>20.795241528820874</v>
       </c>
       <c r="F12" s="0">
-        <v>-4.1889125623967303</v>
+        <v>-4.2047584711791259</v>
       </c>
       <c r="G12" s="0">
-        <v>4.1889125623967303</v>
+        <v>4.2047584711791259</v>
       </c>
       <c r="H12" s="0">
-        <v>20.31108743760327</v>
+        <v>20.295241528820874</v>
       </c>
       <c r="I12" s="0">
-        <v>-4.6889125623967303</v>
+        <v>-4.7047584711791259</v>
       </c>
       <c r="J12" s="0">
-        <v>4.6889125623967303</v>
+        <v>4.7047584711791259</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -974,28 +974,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>675.26099999999997</v>
+        <v>669.91160000000002</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>20.811149684841642</v>
+        <v>20.795313906332336</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.6888503151583585</v>
+        <v>-1.7046860936676644</v>
       </c>
       <c r="G13" s="0">
-        <v>1.6888503151583585</v>
+        <v>1.7046860936676644</v>
       </c>
       <c r="H13" s="0">
-        <v>20.311149684841642</v>
+        <v>20.295313906332336</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.1888503151583585</v>
+        <v>-2.2046860936676644</v>
       </c>
       <c r="J13" s="0">
-        <v>2.1888503151583585</v>
+        <v>2.2046860936676644</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1018,28 +1018,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>674.45989999999995</v>
+        <v>672.01459999999997</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>20.949137742221279</v>
+        <v>20.956595565307072</v>
       </c>
       <c r="F14" s="0">
-        <v>0.44913774222127856</v>
+        <v>0.45659556530707235</v>
       </c>
       <c r="G14" s="0">
-        <v>0.44913774222127856</v>
+        <v>0.45659556530707235</v>
       </c>
       <c r="H14" s="0">
-        <v>20.449137742221279</v>
+        <v>20.456595565307072</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.050862257778721442</v>
+        <v>-0.043404434692927652</v>
       </c>
       <c r="J14" s="0">
-        <v>0.050862257778721442</v>
+        <v>0.043404434692927652</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>0</v>
@@ -1062,28 +1062,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>583.64300000000003</v>
+        <v>585.0598</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.780475086366977</v>
+        <v>20.770486370542606</v>
       </c>
       <c r="F15" s="0">
-        <v>1.2804750863669767</v>
+        <v>1.2704863705426064</v>
       </c>
       <c r="G15" s="0">
-        <v>1.2804750863669767</v>
+        <v>1.2704863705426064</v>
       </c>
       <c r="H15" s="0">
-        <v>20.280475086366977</v>
+        <v>20.270486370542606</v>
       </c>
       <c r="I15" s="0">
-        <v>0.78047508636697671</v>
+        <v>0.77048637054260638</v>
       </c>
       <c r="J15" s="0">
-        <v>0.78047508636697671</v>
+        <v>0.77048637054260638</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -1106,28 +1106,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>617.06880000000001</v>
+        <v>618.17600000000004</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.349894812321025</v>
+        <v>21.370358004268802</v>
       </c>
       <c r="F16" s="0">
-        <v>1.8498948123210255</v>
+        <v>1.8703580042688017</v>
       </c>
       <c r="G16" s="0">
-        <v>1.8498948123210255</v>
+        <v>1.8703580042688017</v>
       </c>
       <c r="H16" s="0">
-        <v>20.849894812321025</v>
+        <v>20.870358004268802</v>
       </c>
       <c r="I16" s="0">
-        <v>1.3498948123210255</v>
+        <v>1.3703580042688017</v>
       </c>
       <c r="J16" s="0">
-        <v>1.3498948123210255</v>
+        <v>1.3703580042688017</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1150,28 +1150,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>1130.2846</v>
+        <v>1122.4987000000001</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>20.915183675906558</v>
+        <v>20.927554259880168</v>
       </c>
       <c r="F17" s="0">
-        <v>2.4151836759065581</v>
+        <v>2.4275542598801678</v>
       </c>
       <c r="G17" s="0">
-        <v>2.4151836759065581</v>
+        <v>2.4275542598801678</v>
       </c>
       <c r="H17" s="0">
-        <v>20.415183675906558</v>
+        <v>20.427554259880168</v>
       </c>
       <c r="I17" s="0">
-        <v>1.9151836759065581</v>
+        <v>1.9275542598801678</v>
       </c>
       <c r="J17" s="0">
-        <v>1.9151836759065581</v>
+        <v>1.9275542598801678</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1194,28 +1194,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>1452.2846</v>
+        <v>1459.4197999999999</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>20.810510658859116</v>
+        <v>20.794141040813074</v>
       </c>
       <c r="F18" s="0">
-        <v>-2.9394893411408845</v>
+        <v>-2.9558589591869264</v>
       </c>
       <c r="G18" s="0">
-        <v>2.9394893411408845</v>
+        <v>2.9558589591869264</v>
       </c>
       <c r="H18" s="0">
-        <v>20.310510658859116</v>
+        <v>20.294141040813074</v>
       </c>
       <c r="I18" s="0">
-        <v>-3.4394893411408845</v>
+        <v>-3.4558589591869264</v>
       </c>
       <c r="J18" s="0">
-        <v>3.4394893411408845</v>
+        <v>3.4558589591869264</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1238,28 +1238,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>668.60829999999999</v>
+        <v>667.94280000000003</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.043814401678489</v>
+        <v>21.037789675738132</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.2061855983215111</v>
+        <v>-1.2122103242618678</v>
       </c>
       <c r="G19" s="0">
-        <v>1.2061855983215111</v>
+        <v>1.2122103242618678</v>
       </c>
       <c r="H19" s="0">
-        <v>20.543814401678489</v>
+        <v>20.537789675738132</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.7061855983215111</v>
+        <v>-1.7122103242618678</v>
       </c>
       <c r="J19" s="0">
-        <v>1.7061855983215111</v>
+        <v>1.7122103242618678</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1282,28 +1282,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>750.32280000000003</v>
+        <v>755.404</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>20.935955851104886</v>
+        <v>21.003416120735715</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.564044148895114</v>
+        <v>-4.4965838792642856</v>
       </c>
       <c r="G20" s="0">
-        <v>4.564044148895114</v>
+        <v>4.4965838792642856</v>
       </c>
       <c r="H20" s="0">
-        <v>20.435955851104886</v>
+        <v>20.503416120735715</v>
       </c>
       <c r="I20" s="0">
-        <v>-5.064044148895114</v>
+        <v>-4.9965838792642856</v>
       </c>
       <c r="J20" s="0">
-        <v>5.064044148895114</v>
+        <v>4.9965838792642856</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1326,28 +1326,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>345.22919999999999</v>
+        <v>344.29160000000002</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>20.826252753434837</v>
+        <v>20.807820564163876</v>
       </c>
       <c r="F21" s="0">
-        <v>-1.6737472465651635</v>
+        <v>-1.692179435836124</v>
       </c>
       <c r="G21" s="0">
-        <v>1.6737472465651635</v>
+        <v>1.692179435836124</v>
       </c>
       <c r="H21" s="0">
-        <v>20.326252753434837</v>
+        <v>20.307820564163876</v>
       </c>
       <c r="I21" s="0">
-        <v>-2.1737472465651635</v>
+        <v>-2.192179435836124</v>
       </c>
       <c r="J21" s="0">
-        <v>2.1737472465651635</v>
+        <v>2.192179435836124</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1370,28 +1370,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>622.22630000000004</v>
+        <v>613.17560000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.957368973517397</v>
+        <v>20.965635406716569</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.54263102648260286</v>
+        <v>-0.53436459328343133</v>
       </c>
       <c r="G22" s="0">
-        <v>0.54263102648260286</v>
+        <v>0.53436459328343133</v>
       </c>
       <c r="H22" s="0">
-        <v>20.457368973517397</v>
+        <v>20.465635406716569</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.0426310264826029</v>
+        <v>-1.0343645932834313</v>
       </c>
       <c r="J22" s="0">
-        <v>1.0426310264826029</v>
+        <v>1.0343645932834313</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1414,28 +1414,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>671.48209999999995</v>
+        <v>674.47910000000002</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>20.999770626511172</v>
+        <v>21.014150079636579</v>
       </c>
       <c r="F23" s="0">
-        <v>0.99977062651117166</v>
+        <v>1.014150079636579</v>
       </c>
       <c r="G23" s="0">
-        <v>0.99977062651117166</v>
+        <v>1.014150079636579</v>
       </c>
       <c r="H23" s="0">
-        <v>20.499770626511172</v>
+        <v>20.514150079636579</v>
       </c>
       <c r="I23" s="0">
-        <v>0.49977062651117166</v>
+        <v>0.51415007963657899</v>
       </c>
       <c r="J23" s="0">
-        <v>0.49977062651117166</v>
+        <v>0.51415007963657899</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1458,28 +1458,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>582.96010000000001</v>
+        <v>577.67240000000004</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>21.275346822489791</v>
+        <v>21.283935803660668</v>
       </c>
       <c r="F24" s="0">
-        <v>1.7753468224897908</v>
+        <v>1.7839358036606683</v>
       </c>
       <c r="G24" s="0">
-        <v>1.7753468224897908</v>
+        <v>1.7839358036606683</v>
       </c>
       <c r="H24" s="0">
-        <v>20.775346822489791</v>
+        <v>20.783935803660668</v>
       </c>
       <c r="I24" s="0">
-        <v>1.2753468224897908</v>
+        <v>1.2839358036606683</v>
       </c>
       <c r="J24" s="0">
-        <v>1.2753468224897908</v>
+        <v>1.2839358036606683</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>1</v>
@@ -1502,28 +1502,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.6952</v>
+        <v>577.55370000000005</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>21.11848881018156</v>
+        <v>21.132170697311839</v>
       </c>
       <c r="F25" s="0">
-        <v>2.6184888101815602</v>
+        <v>2.6321706973118388</v>
       </c>
       <c r="G25" s="0">
-        <v>2.6184888101815602</v>
+        <v>2.6321706973118388</v>
       </c>
       <c r="H25" s="0">
-        <v>20.61848881018156</v>
+        <v>20.632170697311839</v>
       </c>
       <c r="I25" s="0">
-        <v>2.1184888101815602</v>
+        <v>2.1321706973118388</v>
       </c>
       <c r="J25" s="0">
-        <v>2.1184888101815602</v>
+        <v>2.1321706973118388</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1546,28 +1546,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>689.21019999999999</v>
+        <v>688.17229999999995</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>20.828665865862828</v>
+        <v>20.809494739924638</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.42133413413717236</v>
+        <v>-0.44050526007536206</v>
       </c>
       <c r="G26" s="0">
-        <v>0.42133413413717236</v>
+        <v>0.44050526007536206</v>
       </c>
       <c r="H26" s="0">
-        <v>20.328665865862828</v>
+        <v>20.309494739924638</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.92133413413717236</v>
+        <v>-0.94050526007536206</v>
       </c>
       <c r="J26" s="0">
-        <v>0.92133413413717236</v>
+        <v>0.94050526007536206</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>0</v>
@@ -1590,28 +1590,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>641.4787</v>
+        <v>638.71429999999998</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.977824908361427</v>
+        <v>20.988899210687237</v>
       </c>
       <c r="F27" s="0">
-        <v>1.727824908361427</v>
+        <v>1.7388992106872365</v>
       </c>
       <c r="G27" s="0">
-        <v>1.727824908361427</v>
+        <v>1.7388992106872365</v>
       </c>
       <c r="H27" s="0">
-        <v>20.477824908361427</v>
+        <v>20.488899210687237</v>
       </c>
       <c r="I27" s="0">
-        <v>1.227824908361427</v>
+        <v>1.2388992106872365</v>
       </c>
       <c r="J27" s="0">
-        <v>1.227824908361427</v>
+        <v>1.2388992106872365</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1634,28 +1634,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>684.71199999999999</v>
+        <v>676.74940000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>20.940645393817277</v>
+        <v>21.003514478580247</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.80935460618272259</v>
+        <v>-0.74648552141975344</v>
       </c>
       <c r="G28" s="0">
-        <v>0.80935460618272259</v>
+        <v>0.74648552141975344</v>
       </c>
       <c r="H28" s="0">
-        <v>20.440645393817277</v>
+        <v>20.503514478580247</v>
       </c>
       <c r="I28" s="0">
-        <v>-1.3093546061827226</v>
+        <v>-1.2464855214197534</v>
       </c>
       <c r="J28" s="0">
-        <v>1.3093546061827226</v>
+        <v>1.2464855214197534</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1678,28 +1678,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>353.73129999999998</v>
+        <v>354.31049999999999</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>20.994074343974926</v>
+        <v>21.001199947408612</v>
       </c>
       <c r="F29" s="0">
-        <v>0.24407434397492622</v>
+        <v>0.25119994740861174</v>
       </c>
       <c r="G29" s="0">
-        <v>0.24407434397492622</v>
+        <v>0.25119994740861174</v>
       </c>
       <c r="H29" s="0">
-        <v>20.494074343974926</v>
+        <v>20.501199947408612</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.25592565602507378</v>
+        <v>-0.24880005259138827</v>
       </c>
       <c r="J29" s="0">
-        <v>0.25592565602507378</v>
+        <v>0.24880005259138827</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1722,28 +1722,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.46259999999995</v>
+        <v>683.81759999999997</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.180778986771458</v>
+        <v>21.175652676042713</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.31922101322854246</v>
+        <v>-0.32434732395728716</v>
       </c>
       <c r="G30" s="0">
-        <v>0.31922101322854246</v>
+        <v>0.32434732395728716</v>
       </c>
       <c r="H30" s="0">
-        <v>20.680778986771458</v>
+        <v>20.675652676042713</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.81922101322854246</v>
+        <v>-0.82434732395728716</v>
       </c>
       <c r="J30" s="0">
-        <v>0.81922101322854246</v>
+        <v>0.82434732395728716</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1766,28 +1766,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>1356.9842000000001</v>
+        <v>1353.5838000000001</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.420141628001907</v>
+        <v>21.444937157780807</v>
       </c>
       <c r="F31" s="0">
-        <v>1.9201416280019075</v>
+        <v>1.9449371577808066</v>
       </c>
       <c r="G31" s="0">
-        <v>1.9201416280019075</v>
+        <v>1.9449371577808066</v>
       </c>
       <c r="H31" s="0">
-        <v>20.920141628001907</v>
+        <v>20.944937157780807</v>
       </c>
       <c r="I31" s="0">
-        <v>1.4201416280019075</v>
+        <v>1.4449371577808066</v>
       </c>
       <c r="J31" s="0">
-        <v>1.4201416280019075</v>
+        <v>1.4449371577808066</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1810,28 +1810,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>1312.2254</v>
+        <v>1324.2094</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.413013669604958</v>
+        <v>21.439782022413272</v>
       </c>
       <c r="F32" s="0">
-        <v>1.9130136696049576</v>
+        <v>1.9397820224132723</v>
       </c>
       <c r="G32" s="0">
-        <v>1.9130136696049576</v>
+        <v>1.9397820224132723</v>
       </c>
       <c r="H32" s="0">
-        <v>20.913013669604958</v>
+        <v>20.939782022413272</v>
       </c>
       <c r="I32" s="0">
-        <v>1.4130136696049576</v>
+        <v>1.4397820224132723</v>
       </c>
       <c r="J32" s="0">
-        <v>1.4130136696049576</v>
+        <v>1.4397820224132723</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1854,28 +1854,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>1359.0623000000001</v>
+        <v>1370.5188000000001</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.007848192591336</v>
+        <v>20.9906020780634</v>
       </c>
       <c r="F33" s="0">
-        <v>0.0078481925913358452</v>
+        <v>-0.009397921936599829</v>
       </c>
       <c r="G33" s="0">
-        <v>0.0078481925913358452</v>
+        <v>0.009397921936599829</v>
       </c>
       <c r="H33" s="0">
-        <v>20.507848192591336</v>
+        <v>20.4906020780634</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.49215180740866415</v>
+        <v>-0.50939792193659983</v>
       </c>
       <c r="J33" s="0">
-        <v>0.49215180740866415</v>
+        <v>0.50939792193659983</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>0</v>
@@ -1898,28 +1898,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.02089999999998</v>
+        <v>595.53899999999999</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.795091232114626</v>
+        <v>20.782357849622571</v>
       </c>
       <c r="F34" s="0">
-        <v>0.54509123211462551</v>
+        <v>0.53235784962257071</v>
       </c>
       <c r="G34" s="0">
-        <v>0.54509123211462551</v>
+        <v>0.53235784962257071</v>
       </c>
       <c r="H34" s="0">
-        <v>20.295091232114626</v>
+        <v>20.282357849622571</v>
       </c>
       <c r="I34" s="0">
-        <v>0.045091232114625512</v>
+        <v>0.032357849622570711</v>
       </c>
       <c r="J34" s="0">
-        <v>0.045091232114625512</v>
+        <v>0.032357849622570711</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>1</v>
@@ -1942,28 +1942,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>623.09130000000005</v>
+        <v>620.18640000000005</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>21.095185626456637</v>
+        <v>21.102616475182231</v>
       </c>
       <c r="F35" s="0">
-        <v>-0.40481437354336336</v>
+        <v>-0.39738352481776928</v>
       </c>
       <c r="G35" s="0">
-        <v>0.40481437354336336</v>
+        <v>0.39738352481776928</v>
       </c>
       <c r="H35" s="0">
-        <v>20.595185626456637</v>
+        <v>20.602616475182231</v>
       </c>
       <c r="I35" s="0">
-        <v>-0.90481437354336336</v>
+        <v>-0.89738352481776929</v>
       </c>
       <c r="J35" s="0">
-        <v>0.90481437354336336</v>
+        <v>0.89738352481776929</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1986,28 +1986,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>590.04459999999995</v>
+        <v>589.86860000000001</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>21.094610418665862</v>
+        <v>21.102045556971554</v>
       </c>
       <c r="F36" s="0">
-        <v>1.5946104186658623</v>
+        <v>1.6020455569715537</v>
       </c>
       <c r="G36" s="0">
-        <v>1.5946104186658623</v>
+        <v>1.6020455569715537</v>
       </c>
       <c r="H36" s="0">
-        <v>20.594610418665862</v>
+        <v>20.602045556971554</v>
       </c>
       <c r="I36" s="0">
-        <v>1.0946104186658623</v>
+        <v>1.1020455569715537</v>
       </c>
       <c r="J36" s="0">
-        <v>1.0946104186658623</v>
+        <v>1.1020455569715537</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>1</v>
@@ -2030,28 +2030,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.99620000000004</v>
+        <v>724.63610000000006</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>20.975506380429408</v>
+        <v>20.987737542789144</v>
       </c>
       <c r="F37" s="0">
-        <v>-4.0244936195705918</v>
+        <v>-4.0122624572108556</v>
       </c>
       <c r="G37" s="0">
-        <v>4.0244936195705918</v>
+        <v>4.0122624572108556</v>
       </c>
       <c r="H37" s="0">
-        <v>20.475506380429408</v>
+        <v>20.487737542789144</v>
       </c>
       <c r="I37" s="0">
-        <v>-4.5244936195705918</v>
+        <v>-4.5122624572108556</v>
       </c>
       <c r="J37" s="0">
-        <v>4.5244936195705918</v>
+        <v>4.5122624572108556</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2074,28 +2074,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>600.44100000000003</v>
+        <v>598.2287</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>20.940722108190513</v>
+        <v>21.003521492488353</v>
       </c>
       <c r="F38" s="0">
-        <v>1.9407221081905135</v>
+        <v>2.0035214924883533</v>
       </c>
       <c r="G38" s="0">
-        <v>1.9407221081905135</v>
+        <v>2.0035214924883533</v>
       </c>
       <c r="H38" s="0">
-        <v>20.440722108190513</v>
+        <v>20.503521492488353</v>
       </c>
       <c r="I38" s="0">
-        <v>1.4407221081905135</v>
+        <v>1.5035214924883533</v>
       </c>
       <c r="J38" s="0">
-        <v>1.4407221081905135</v>
+        <v>1.5035214924883533</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2118,28 +2118,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>692.81489999999997</v>
+        <v>681.9153</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.784361432158423</v>
+        <v>20.773573810543194</v>
       </c>
       <c r="F39" s="0">
-        <v>1.7843614321584234</v>
+        <v>1.7735738105431942</v>
       </c>
       <c r="G39" s="0">
-        <v>1.7843614321584234</v>
+        <v>1.7735738105431942</v>
       </c>
       <c r="H39" s="0">
-        <v>20.284361432158423</v>
+        <v>20.273573810543194</v>
       </c>
       <c r="I39" s="0">
-        <v>1.2843614321584234</v>
+        <v>1.2735738105431942</v>
       </c>
       <c r="J39" s="0">
-        <v>1.2843614321584234</v>
+        <v>1.2735738105431942</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2162,28 +2162,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>1193.8898999999999</v>
+        <v>1171.8478</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>21.104093763777893</v>
+        <v>21.080122903846071</v>
       </c>
       <c r="F40" s="0">
-        <v>0.10409376377789314</v>
+        <v>0.080122903846071125</v>
       </c>
       <c r="G40" s="0">
-        <v>0.10409376377789314</v>
+        <v>0.080122903846071125</v>
       </c>
       <c r="H40" s="0">
-        <v>20.604093763777893</v>
+        <v>20.580122903846071</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.39590623622210686</v>
+        <v>-0.41987709615392888</v>
       </c>
       <c r="J40" s="0">
-        <v>0.39590623622210686</v>
+        <v>0.41987709615392888</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>0</v>
@@ -2206,28 +2206,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>666.36320000000001</v>
+        <v>665.75360000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.115876062014799</v>
+        <v>21.101100837816599</v>
       </c>
       <c r="F41" s="0">
-        <v>0.61587606201479872</v>
+        <v>0.60110083781659895</v>
       </c>
       <c r="G41" s="0">
-        <v>0.61587606201479872</v>
+        <v>0.60110083781659895</v>
       </c>
       <c r="H41" s="0">
-        <v>20.615876062014799</v>
+        <v>20.601100837816599</v>
       </c>
       <c r="I41" s="0">
-        <v>0.11587606201479872</v>
+        <v>0.10110083781659895</v>
       </c>
       <c r="J41" s="0">
-        <v>0.11587606201479872</v>
+        <v>0.10110083781659895</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2250,28 +2250,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>340.92939999999999</v>
+        <v>343.99220000000003</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>21.028470461453068</v>
+        <v>21.040191709581929</v>
       </c>
       <c r="F42" s="0">
-        <v>1.7784704614530682</v>
+        <v>1.7901917095819293</v>
       </c>
       <c r="G42" s="0">
-        <v>1.7784704614530682</v>
+        <v>1.7901917095819293</v>
       </c>
       <c r="H42" s="0">
-        <v>20.528470461453068</v>
+        <v>20.540191709581929</v>
       </c>
       <c r="I42" s="0">
-        <v>1.2784704614530682</v>
+        <v>1.2901917095819293</v>
       </c>
       <c r="J42" s="0">
-        <v>1.2784704614530682</v>
+        <v>1.2901917095819293</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>1</v>
@@ -2294,28 +2294,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>582.97400000000005</v>
+        <v>584.32039999999995</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>20.945889542337941</v>
+        <v>21.003624449799588</v>
       </c>
       <c r="F43" s="0">
-        <v>0.94588954233794098</v>
+        <v>1.0036244497995881</v>
       </c>
       <c r="G43" s="0">
-        <v>0.94588954233794098</v>
+        <v>1.0036244497995881</v>
       </c>
       <c r="H43" s="0">
-        <v>20.445889542337941</v>
+        <v>20.503624449799588</v>
       </c>
       <c r="I43" s="0">
-        <v>0.44588954233794098</v>
+        <v>0.50362444979958809</v>
       </c>
       <c r="J43" s="0">
-        <v>0.44588954233794098</v>
+        <v>0.50362444979958809</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>1</v>
@@ -2338,28 +2338,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>657.05769999999996</v>
+        <v>660.15719999999999</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>20.800410879068494</v>
+        <v>20.78660828283418</v>
       </c>
       <c r="F44" s="0">
-        <v>0.80041087906849384</v>
+        <v>0.78660828283418027</v>
       </c>
       <c r="G44" s="0">
-        <v>0.80041087906849384</v>
+        <v>0.78660828283418027</v>
       </c>
       <c r="H44" s="0">
-        <v>20.300410879068494</v>
+        <v>20.28660828283418</v>
       </c>
       <c r="I44" s="0">
-        <v>0.30041087906849384</v>
+        <v>0.28660828283418027</v>
       </c>
       <c r="J44" s="0">
-        <v>0.30041087906849384</v>
+        <v>0.28660828283418027</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2382,28 +2382,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>584.81910000000005</v>
+        <v>581.95590000000004</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>21.106568407420316</v>
+        <v>21.117078755193056</v>
       </c>
       <c r="F45" s="0">
-        <v>1.1065684074203155</v>
+        <v>1.1170787551930559</v>
       </c>
       <c r="G45" s="0">
-        <v>1.1065684074203155</v>
+        <v>1.1170787551930559</v>
       </c>
       <c r="H45" s="0">
-        <v>20.606568407420316</v>
+        <v>20.617078755193056</v>
       </c>
       <c r="I45" s="0">
-        <v>0.60656840742031548</v>
+        <v>0.61707875519305588</v>
       </c>
       <c r="J45" s="0">
-        <v>0.60656840742031548</v>
+        <v>0.61707875519305588</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>1</v>
@@ -2426,28 +2426,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>1457.3396</v>
+        <v>1432.1427000000001</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>20.830726709229882</v>
+        <v>20.810571632932547</v>
       </c>
       <c r="F46" s="0">
-        <v>-1.1692732907701178</v>
+        <v>-1.1894283670674533</v>
       </c>
       <c r="G46" s="0">
-        <v>1.1692732907701178</v>
+        <v>1.1894283670674533</v>
       </c>
       <c r="H46" s="0">
-        <v>20.330726709229882</v>
+        <v>20.310571632932547</v>
       </c>
       <c r="I46" s="0">
-        <v>-1.6692732907701178</v>
+        <v>-1.6894283670674533</v>
       </c>
       <c r="J46" s="0">
-        <v>1.6692732907701178</v>
+        <v>1.6894283670674533</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2470,28 +2470,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>1394.6958999999999</v>
+        <v>1393.6792</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>20.830778842146366</v>
+        <v>20.810629094658204</v>
       </c>
       <c r="F47" s="0">
-        <v>-1.1692211578536345</v>
+        <v>-1.1893709053417965</v>
       </c>
       <c r="G47" s="0">
-        <v>1.1692211578536345</v>
+        <v>1.1893709053417965</v>
       </c>
       <c r="H47" s="0">
-        <v>20.330778842146366</v>
+        <v>20.310629094658204</v>
       </c>
       <c r="I47" s="0">
-        <v>-1.6692211578536345</v>
+        <v>-1.6893709053417965</v>
       </c>
       <c r="J47" s="0">
-        <v>1.6692211578536345</v>
+        <v>1.6893709053417965</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2514,28 +2514,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>1393.5521000000001</v>
+        <v>1418.9514999999999</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.116624635870785</v>
+        <v>21.12777341289566</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.8833753641292148</v>
+        <v>-1.8722265871043398</v>
       </c>
       <c r="G48" s="0">
-        <v>1.8833753641292148</v>
+        <v>1.8722265871043398</v>
       </c>
       <c r="H48" s="0">
-        <v>20.616624635870785</v>
+        <v>20.62777341289566</v>
       </c>
       <c r="I48" s="0">
-        <v>-2.3833753641292148</v>
+        <v>-2.3722265871043398</v>
       </c>
       <c r="J48" s="0">
-        <v>2.3833753641292148</v>
+        <v>2.3722265871043398</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2558,28 +2558,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>1328.9452000000001</v>
+        <v>1319.8444999999999</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>21.075341325402466</v>
+        <v>21.075305398992192</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.67465867459753426</v>
+        <v>-0.67469460100780765</v>
       </c>
       <c r="G49" s="0">
-        <v>0.67465867459753426</v>
+        <v>0.67469460100780765</v>
       </c>
       <c r="H49" s="0">
-        <v>20.575341325402466</v>
+        <v>20.575305398992192</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.1746586745975343</v>
+        <v>-1.1746946010078077</v>
       </c>
       <c r="J49" s="0">
-        <v>1.1746586745975343</v>
+        <v>1.1746946010078077</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2602,28 +2602,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>1373.3529000000001</v>
+        <v>1370.9471000000001</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>20.938821848736971</v>
+        <v>21.00342689770892</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.56117815126302872</v>
+        <v>-0.4965731022910802</v>
       </c>
       <c r="G50" s="0">
-        <v>0.56117815126302872</v>
+        <v>0.4965731022910802</v>
       </c>
       <c r="H50" s="0">
-        <v>20.438821848736971</v>
+        <v>20.50342689770892</v>
       </c>
       <c r="I50" s="0">
-        <v>-1.0611781512630287</v>
+        <v>-0.9965731022910802</v>
       </c>
       <c r="J50" s="0">
-        <v>1.0611781512630287</v>
+        <v>0.9965731022910802</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2646,28 +2646,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>1232.3471999999999</v>
+        <v>1230.9086</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>21.283136021096464</v>
+        <v>21.289007247266369</v>
       </c>
       <c r="F51" s="0">
-        <v>2.0831360210964647</v>
+        <v>2.0890072472663697</v>
       </c>
       <c r="G51" s="0">
-        <v>2.0831360210964647</v>
+        <v>2.0890072472663697</v>
       </c>
       <c r="H51" s="0">
-        <v>20.783136021096464</v>
+        <v>20.789007247266369</v>
       </c>
       <c r="I51" s="0">
-        <v>1.5831360210964647</v>
+        <v>1.5890072472663697</v>
       </c>
       <c r="J51" s="0">
-        <v>1.5831360210964647</v>
+        <v>1.5890072472663697</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2690,28 +2690,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>1151.9466</v>
+        <v>1142.3658</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>21.072262043517888</v>
+        <v>21.071965201198314</v>
       </c>
       <c r="F52" s="0">
-        <v>3.5722620435178882</v>
+        <v>3.5719652011983136</v>
       </c>
       <c r="G52" s="0">
-        <v>3.5722620435178882</v>
+        <v>3.5719652011983136</v>
       </c>
       <c r="H52" s="0">
-        <v>20.572262043517888</v>
+        <v>20.571965201198314</v>
       </c>
       <c r="I52" s="0">
-        <v>3.0722620435178882</v>
+        <v>3.0719652011983136</v>
       </c>
       <c r="J52" s="0">
-        <v>3.0722620435178882</v>
+        <v>3.0719652011983136</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2734,28 +2734,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>1179.067</v>
+        <v>1183.6578999999999</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>20.91922244743499</v>
+        <v>20.931955269114045</v>
       </c>
       <c r="F53" s="0">
-        <v>2.5192224474349914</v>
+        <v>2.5319552691140466</v>
       </c>
       <c r="G53" s="0">
-        <v>2.5192224474349914</v>
+        <v>2.5319552691140466</v>
       </c>
       <c r="H53" s="0">
-        <v>20.41922244743499</v>
+        <v>20.431955269114045</v>
       </c>
       <c r="I53" s="0">
-        <v>2.0192224474349914</v>
+        <v>2.0319552691140466</v>
       </c>
       <c r="J53" s="0">
-        <v>2.0192224474349914</v>
+        <v>2.0319552691140466</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2778,28 +2778,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>1127.4477999999999</v>
+        <v>1127.7965999999999</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>20.939532800281047</v>
+        <v>21.003458715916942</v>
       </c>
       <c r="F54" s="0">
-        <v>1.9395328002810466</v>
+        <v>2.0034587159169419</v>
       </c>
       <c r="G54" s="0">
-        <v>1.9395328002810466</v>
+        <v>2.0034587159169419</v>
       </c>
       <c r="H54" s="0">
-        <v>20.439532800281047</v>
+        <v>20.503458715916942</v>
       </c>
       <c r="I54" s="0">
-        <v>1.4395328002810466</v>
+        <v>1.5034587159169419</v>
       </c>
       <c r="J54" s="0">
-        <v>1.4395328002810466</v>
+        <v>1.5034587159169419</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2822,28 +2822,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.82780000000002</v>
+        <v>600.21460000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>20.937051699249306</v>
+        <v>21.003449475248658</v>
       </c>
       <c r="F55" s="0">
-        <v>1.4370516992493059</v>
+        <v>1.503449475248658</v>
       </c>
       <c r="G55" s="0">
-        <v>1.4370516992493059</v>
+        <v>1.503449475248658</v>
       </c>
       <c r="H55" s="0">
-        <v>20.437051699249306</v>
+        <v>20.503449475248658</v>
       </c>
       <c r="I55" s="0">
-        <v>0.93705169924930587</v>
+        <v>1.003449475248658</v>
       </c>
       <c r="J55" s="0">
-        <v>0.93705169924930587</v>
+        <v>1.003449475248658</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2866,28 +2866,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>727.90769999999998</v>
+        <v>684.51480000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>20.850154824984358</v>
+        <v>20.826953127794582</v>
       </c>
       <c r="F56" s="0">
-        <v>0.35015482498435802</v>
+        <v>0.32695312779458163</v>
       </c>
       <c r="G56" s="0">
-        <v>0.35015482498435802</v>
+        <v>0.32695312779458163</v>
       </c>
       <c r="H56" s="0">
-        <v>20.350154824984358</v>
+        <v>20.326953127794582</v>
       </c>
       <c r="I56" s="0">
-        <v>-0.14984517501564198</v>
+        <v>-0.17304687220541837</v>
       </c>
       <c r="J56" s="0">
-        <v>0.14984517501564198</v>
+        <v>0.17304687220541837</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>0</v>
@@ -2910,28 +2910,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>646.02480000000003</v>
+        <v>632.78740000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>21.03941981439791</v>
+        <v>21.032088122911066</v>
       </c>
       <c r="F57" s="0">
-        <v>0.039419814397909647</v>
+        <v>0.032088122911066108</v>
       </c>
       <c r="G57" s="0">
-        <v>0.039419814397909647</v>
+        <v>0.032088122911066108</v>
       </c>
       <c r="H57" s="0">
-        <v>20.53941981439791</v>
+        <v>20.532088122911066</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.46058018560209035</v>
+        <v>-0.46791187708893389</v>
       </c>
       <c r="J57" s="0">
-        <v>0.46058018560209035</v>
+        <v>0.46791187708893389</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2954,28 +2954,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>1120.8548000000001</v>
+        <v>1105.7334000000001</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>20.917491820357068</v>
+        <v>20.930757399296425</v>
       </c>
       <c r="F58" s="0">
-        <v>-2.5825081796429323</v>
+        <v>-2.5692426007035749</v>
       </c>
       <c r="G58" s="0">
-        <v>2.5825081796429323</v>
+        <v>2.5692426007035749</v>
       </c>
       <c r="H58" s="0">
-        <v>20.417491820357068</v>
+        <v>20.430757399296425</v>
       </c>
       <c r="I58" s="0">
-        <v>-3.0825081796429323</v>
+        <v>-3.0692426007035749</v>
       </c>
       <c r="J58" s="0">
-        <v>3.0825081796429323</v>
+        <v>3.0692426007035749</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2998,28 +2998,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.77250000000004</v>
+        <v>665.27829999999995</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.067676895585699</v>
+        <v>21.045846146554705</v>
       </c>
       <c r="F59" s="0">
-        <v>0.56767689558569856</v>
+        <v>0.54584614655470531</v>
       </c>
       <c r="G59" s="0">
-        <v>0.56767689558569856</v>
+        <v>0.54584614655470531</v>
       </c>
       <c r="H59" s="0">
-        <v>20.567676895585699</v>
+        <v>20.545846146554705</v>
       </c>
       <c r="I59" s="0">
-        <v>0.06767689558569856</v>
+        <v>0.045846146554705314</v>
       </c>
       <c r="J59" s="0">
-        <v>0.06767689558569856</v>
+        <v>0.045846146554705314</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3042,28 +3042,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>695.50199999999995</v>
+        <v>655.14710000000002</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>20.943766984021561</v>
+        <v>21.003579286366666</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.55623301597843877</v>
+        <v>-0.49642071363333429</v>
       </c>
       <c r="G60" s="0">
-        <v>0.55623301597843877</v>
+        <v>0.49642071363333429</v>
       </c>
       <c r="H60" s="0">
-        <v>20.443766984021561</v>
+        <v>20.503579286366666</v>
       </c>
       <c r="I60" s="0">
-        <v>-1.0562330159784388</v>
+        <v>-0.99642071363333429</v>
       </c>
       <c r="J60" s="0">
-        <v>1.0562330159784388</v>
+        <v>0.99642071363333429</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3086,28 +3086,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>639.4633</v>
+        <v>642.19590000000005</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.952878878779856</v>
+        <v>20.959634958298267</v>
       </c>
       <c r="F61" s="0">
-        <v>0.95287887877985611</v>
+        <v>0.95963495829826684</v>
       </c>
       <c r="G61" s="0">
-        <v>0.95287887877985611</v>
+        <v>0.95963495829826684</v>
       </c>
       <c r="H61" s="0">
-        <v>20.452878878779856</v>
+        <v>20.459634958298267</v>
       </c>
       <c r="I61" s="0">
-        <v>0.45287887877985611</v>
+        <v>0.45963495829826684</v>
       </c>
       <c r="J61" s="0">
-        <v>0.45287887877985611</v>
+        <v>0.45963495829826684</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3130,28 +3130,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>699.43420000000003</v>
+        <v>671.02829999999995</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>20.951758430406851</v>
+        <v>20.962775383513446</v>
       </c>
       <c r="F62" s="0">
-        <v>-2.0482415695931486</v>
+        <v>-2.0372246164865544</v>
       </c>
       <c r="G62" s="0">
-        <v>2.0482415695931486</v>
+        <v>2.0372246164865544</v>
       </c>
       <c r="H62" s="0">
-        <v>20.451758430406851</v>
+        <v>20.462775383513446</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.5482415695931486</v>
+        <v>-2.5372246164865544</v>
       </c>
       <c r="J62" s="0">
-        <v>2.5482415695931486</v>
+        <v>2.5372246164865544</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3174,28 +3174,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>683.36609999999996</v>
+        <v>658.74609999999996</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>20.799048126730945</v>
+        <v>20.785522729548532</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.70095187326905517</v>
+        <v>-0.71447727045146792</v>
       </c>
       <c r="G63" s="0">
-        <v>0.70095187326905517</v>
+        <v>0.71447727045146792</v>
       </c>
       <c r="H63" s="0">
-        <v>20.299048126730945</v>
+        <v>20.285522729548532</v>
       </c>
       <c r="I63" s="0">
-        <v>-1.2009518732690552</v>
+        <v>-1.2144772704514679</v>
       </c>
       <c r="J63" s="0">
-        <v>1.2009518732690552</v>
+        <v>1.2144772704514679</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3218,28 +3218,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>421.81869999999998</v>
+        <v>418.81540000000001</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.939403401197598</v>
+        <v>21.003509091462448</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.5605965988024018</v>
+        <v>-1.4964909085375524</v>
       </c>
       <c r="G64" s="0">
-        <v>1.5605965988024018</v>
+        <v>1.4964909085375524</v>
       </c>
       <c r="H64" s="0">
-        <v>20.439403401197598</v>
+        <v>20.503509091462448</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.0605965988024018</v>
+        <v>-1.9964909085375524</v>
       </c>
       <c r="J64" s="0">
-        <v>2.0605965988024018</v>
+        <v>1.9964909085375524</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3262,28 +3262,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>594.92830000000004</v>
+        <v>593.42259999999999</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>20.934487547083808</v>
+        <v>20.893790247983933</v>
       </c>
       <c r="F65" s="0">
-        <v>1.6844875470838083</v>
+        <v>1.643790247983933</v>
       </c>
       <c r="G65" s="0">
-        <v>1.6844875470838083</v>
+        <v>1.643790247983933</v>
       </c>
       <c r="H65" s="0">
-        <v>20.434487547083808</v>
+        <v>20.393790247983933</v>
       </c>
       <c r="I65" s="0">
-        <v>1.1844875470838083</v>
+        <v>1.143790247983933</v>
       </c>
       <c r="J65" s="0">
-        <v>1.1844875470838083</v>
+        <v>1.143790247983933</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3306,28 +3306,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>672.91949999999997</v>
+        <v>709.44029999999998</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.067943928866061</v>
+        <v>21.068876605698904</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.432056071133939</v>
+        <v>-2.4311233943010961</v>
       </c>
       <c r="G66" s="0">
-        <v>2.432056071133939</v>
+        <v>2.4311233943010961</v>
       </c>
       <c r="H66" s="0">
-        <v>20.567943928866061</v>
+        <v>20.568876605698904</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.932056071133939</v>
+        <v>-2.9311233943010962</v>
       </c>
       <c r="J66" s="0">
-        <v>2.932056071133939</v>
+        <v>2.9311233943010962</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3350,28 +3350,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>637.33479999999997</v>
+        <v>625.83199999999999</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>21.067325097066693</v>
+        <v>21.067303670408336</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.43267490293330724</v>
+        <v>-0.43269632959166415</v>
       </c>
       <c r="G67" s="0">
-        <v>0.43267490293330724</v>
+        <v>0.43269632959166415</v>
       </c>
       <c r="H67" s="0">
-        <v>20.567325097066693</v>
+        <v>20.567303670408336</v>
       </c>
       <c r="I67" s="0">
-        <v>-0.93267490293330724</v>
+        <v>-0.93269632959166415</v>
       </c>
       <c r="J67" s="0">
-        <v>0.93267490293330724</v>
+        <v>0.93269632959166415</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3394,28 +3394,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>879.03800000000001</v>
+        <v>889.9828</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>21.067515281555739</v>
+        <v>21.067216412761553</v>
       </c>
       <c r="F68" s="0">
-        <v>2.0675152815557389</v>
+        <v>2.0672164127615531</v>
       </c>
       <c r="G68" s="0">
-        <v>2.0675152815557389</v>
+        <v>2.0672164127615531</v>
       </c>
       <c r="H68" s="0">
-        <v>20.567515281555739</v>
+        <v>20.567216412761553</v>
       </c>
       <c r="I68" s="0">
-        <v>1.5675152815557389</v>
+        <v>1.5672164127615531</v>
       </c>
       <c r="J68" s="0">
-        <v>1.5675152815557389</v>
+        <v>1.5672164127615531</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3476,16 +3476,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.46</v>
+        <v>1.4590000000000001</v>
       </c>
       <c r="C2" s="0">
         <v>1.811</v>
       </c>
       <c r="D2" s="0">
-        <v>0.025000000000000001</v>
+        <v>0.023</v>
       </c>
       <c r="E2" s="0">
-        <v>0.036999999999999998</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3495,22 +3495,22 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0.014999999999999999</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="C3" s="0">
+        <v>0.0080000000000000002</v>
+      </c>
+      <c r="D3" s="0">
         <v>0.012999999999999999</v>
       </c>
-      <c r="D3" s="0">
-        <v>0.016</v>
-      </c>
       <c r="E3" s="0">
-        <v>0.031</v>
+        <v>0.042999999999999997</v>
       </c>
       <c r="F3" s="0">
-        <v>1.2</v>
+        <v>2.3999999999999999</v>
       </c>
       <c r="G3" s="0">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3529,18 +3529,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.474</v>
+        <v>1.478</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.46300000000000002</v>
+        <v>-0.47899999999999998</v>
       </c>
       <c r="F5" s="0">
-        <v>38.799999999999997</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>43.399999999999999</v>
+        <v>42.799999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -3548,10 +3548,10 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.4530000000000001</v>
+        <v>1.4550000000000001</v>
       </c>
       <c r="C6" s="0">
-        <v>1.8140000000000001</v>
+        <v>1.815</v>
       </c>
       <c r="D6" s="0">
         <v>0.001</v>
@@ -3567,7 +3567,7 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.5069999999999999</v>
+        <v>1.51</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
@@ -3578,7 +3578,7 @@
         <v>37.299999999999997</v>
       </c>
       <c r="G7" s="0">
-        <v>38.799999999999997</v>
+        <v>40.299999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -3688,13 +3688,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>21.5322</v>
+        <v>21.556100000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>0.80740000000000001</v>
+        <v>0.80569999999999997</v>
       </c>
       <c r="D2" s="0">
-        <v>26.667999999999999</v>
+        <v>26.753</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3711,10 +3711,10 @@
         <v>0.00069999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>0.441</v>
+        <v>0.40000000000000002</v>
       </c>
       <c r="E3" s="0">
-        <v>0.66090000000000004</v>
+        <v>0.69079999999999997</v>
       </c>
     </row>
     <row r="4">
@@ -3728,10 +3728,10 @@
         <v>0.0132</v>
       </c>
       <c r="D4" s="0">
-        <v>-1.4510000000000001</v>
+        <v>-1.4490000000000001</v>
       </c>
       <c r="E4" s="0">
-        <v>0.15179999999999999</v>
+        <v>0.15210000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/預測結果與評估指標_kfold_mask幾何_年齡.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_年齡.xlsx
@@ -427,7 +427,7 @@
     <col min="3" max="3" width="13.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="15.42578125" customWidth="true"/>
+    <col min="6" max="6" width="14.42578125" customWidth="true"/>
     <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="17" customWidth="true"/>
     <col min="9" max="9" width="20.5703125" customWidth="true"/>
@@ -490,28 +490,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>405.481</v>
+        <v>408.47719999999998</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>21.003471696046692</v>
+        <v>21.087676430752779</v>
       </c>
       <c r="F2" s="0">
-        <v>-1.9965283039533084</v>
+        <v>-1.9123235692472207</v>
       </c>
       <c r="G2" s="0">
-        <v>1.9965283039533084</v>
+        <v>1.9123235692472207</v>
       </c>
       <c r="H2" s="0">
-        <v>20.503471696046692</v>
+        <v>20.587676430752779</v>
       </c>
       <c r="I2" s="0">
-        <v>-2.4965283039533084</v>
+        <v>-2.4123235692472207</v>
       </c>
       <c r="J2" s="0">
-        <v>2.4965283039533084</v>
+        <v>2.4123235692472207</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -534,28 +534,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.36530000000005</v>
+        <v>618.74630000000002</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>21.391752160002106</v>
+        <v>21.347894703438986</v>
       </c>
       <c r="F3" s="0">
-        <v>0.39175216000210611</v>
+        <v>0.34789470343898543</v>
       </c>
       <c r="G3" s="0">
-        <v>0.39175216000210611</v>
+        <v>0.34789470343898543</v>
       </c>
       <c r="H3" s="0">
-        <v>20.891752160002106</v>
+        <v>20.847894703438986</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.10824783999789389</v>
+        <v>-0.15210529656101457</v>
       </c>
       <c r="J3" s="0">
-        <v>0.10824783999789389</v>
+        <v>0.15210529656101457</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -578,28 +578,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>740.86210000000005</v>
+        <v>757.2885</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>21.024082766863774</v>
+        <v>21.025824455088156</v>
       </c>
       <c r="F4" s="0">
-        <v>-2.4759172331362258</v>
+        <v>-2.4741755449118443</v>
       </c>
       <c r="G4" s="0">
-        <v>2.4759172331362258</v>
+        <v>2.4741755449118443</v>
       </c>
       <c r="H4" s="0">
-        <v>20.524082766863774</v>
+        <v>20.525824455088156</v>
       </c>
       <c r="I4" s="0">
-        <v>-2.9759172331362258</v>
+        <v>-2.9741755449118443</v>
       </c>
       <c r="J4" s="0">
-        <v>2.9759172331362258</v>
+        <v>2.9741755449118443</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -622,28 +622,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>580.86249999999996</v>
+        <v>583.17809999999997</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>21.003634692687584</v>
+        <v>20.820584416761914</v>
       </c>
       <c r="F5" s="0">
-        <v>0.0036346926875836516</v>
+        <v>-0.17941558323808593</v>
       </c>
       <c r="G5" s="0">
-        <v>0.0036346926875836516</v>
+        <v>0.17941558323808593</v>
       </c>
       <c r="H5" s="0">
-        <v>20.503634692687584</v>
+        <v>20.320584416761914</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.49636530731241635</v>
+        <v>-0.67941558323808593</v>
       </c>
       <c r="J5" s="0">
-        <v>0.49636530731241635</v>
+        <v>0.67941558323808593</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -666,28 +666,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>620.73389999999995</v>
+        <v>633.10580000000004</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.418053005341442</v>
+        <v>21.372009345019151</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.081946994658558481</v>
+        <v>-0.12799065498084872</v>
       </c>
       <c r="G6" s="0">
-        <v>0.081946994658558481</v>
+        <v>0.12799065498084872</v>
       </c>
       <c r="H6" s="0">
-        <v>20.918053005341442</v>
+        <v>20.872009345019151</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.58194699465855848</v>
+        <v>-0.62799065498084872</v>
       </c>
       <c r="J6" s="0">
-        <v>0.58194699465855848</v>
+        <v>0.62799065498084872</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -710,28 +710,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>711.67399999999998</v>
+        <v>712.21130000000005</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.003415319883146</v>
+        <v>21.238998525824698</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.99658468011685386</v>
+        <v>-0.76100147417530195</v>
       </c>
       <c r="G7" s="0">
-        <v>0.99658468011685386</v>
+        <v>0.76100147417530195</v>
       </c>
       <c r="H7" s="0">
-        <v>20.503415319883146</v>
+        <v>20.738998525824698</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.4965846801168539</v>
+        <v>-1.261001474175302</v>
       </c>
       <c r="J7" s="0">
-        <v>1.4965846801168539</v>
+        <v>1.261001474175302</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -754,28 +754,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>757.66719999999998</v>
+        <v>765.37739999999997</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>21.175926585647883</v>
+        <v>20.91686113068959</v>
       </c>
       <c r="F8" s="0">
-        <v>-3.8240734143521173</v>
+        <v>-4.0831388693104103</v>
       </c>
       <c r="G8" s="0">
-        <v>3.8240734143521173</v>
+        <v>4.0831388693104103</v>
       </c>
       <c r="H8" s="0">
-        <v>20.675926585647883</v>
+        <v>20.41686113068959</v>
       </c>
       <c r="I8" s="0">
-        <v>-4.3240734143521173</v>
+        <v>-4.5831388693104103</v>
       </c>
       <c r="J8" s="0">
-        <v>4.3240734143521173</v>
+        <v>4.5831388693104103</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -798,28 +798,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>390.43310000000002</v>
+        <v>384.85610000000003</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>20.966493622312711</v>
+        <v>20.929935856059341</v>
       </c>
       <c r="F9" s="0">
-        <v>0.46649362231271141</v>
+        <v>0.42993585605934115</v>
       </c>
       <c r="G9" s="0">
-        <v>0.46649362231271141</v>
+        <v>0.42993585605934115</v>
       </c>
       <c r="H9" s="0">
-        <v>20.466493622312711</v>
+        <v>20.429935856059341</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.033506377687288591</v>
+        <v>-0.070064143940658852</v>
       </c>
       <c r="J9" s="0">
-        <v>0.033506377687288591</v>
+        <v>0.070064143940658852</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -842,28 +842,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>1263.4103</v>
+        <v>1296.7855999999999</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.247105366409329</v>
+        <v>21.140336443137404</v>
       </c>
       <c r="F10" s="0">
-        <v>0.24710536640932901</v>
+        <v>0.14033644313740368</v>
       </c>
       <c r="G10" s="0">
-        <v>0.24710536640932901</v>
+        <v>0.14033644313740368</v>
       </c>
       <c r="H10" s="0">
-        <v>20.747105366409329</v>
+        <v>20.640336443137404</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.25289463359067099</v>
+        <v>-0.35966355686259632</v>
       </c>
       <c r="J10" s="0">
-        <v>0.25289463359067099</v>
+        <v>0.35966355686259632</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -886,28 +886,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>319.74869999999999</v>
+        <v>320.06220000000002</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>21.003525317817989</v>
+        <v>20.986317278070693</v>
       </c>
       <c r="F11" s="0">
-        <v>3.0035253178179886</v>
+        <v>2.9863172780706932</v>
       </c>
       <c r="G11" s="0">
-        <v>3.0035253178179886</v>
+        <v>2.9863172780706932</v>
       </c>
       <c r="H11" s="0">
-        <v>20.503525317817989</v>
+        <v>20.486317278070693</v>
       </c>
       <c r="I11" s="0">
-        <v>2.5035253178179886</v>
+        <v>2.4863172780706932</v>
       </c>
       <c r="J11" s="0">
-        <v>2.5035253178179886</v>
+        <v>2.4863172780706932</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -930,28 +930,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>718.36379999999997</v>
+        <v>747.66359999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>20.795241528820874</v>
+        <v>20.857507749902062</v>
       </c>
       <c r="F12" s="0">
-        <v>-4.2047584711791259</v>
+        <v>-4.1424922500979378</v>
       </c>
       <c r="G12" s="0">
-        <v>4.2047584711791259</v>
+        <v>4.1424922500979378</v>
       </c>
       <c r="H12" s="0">
-        <v>20.295241528820874</v>
+        <v>20.357507749902062</v>
       </c>
       <c r="I12" s="0">
-        <v>-4.7047584711791259</v>
+        <v>-4.6424922500979378</v>
       </c>
       <c r="J12" s="0">
-        <v>4.7047584711791259</v>
+        <v>4.6424922500979378</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -974,28 +974,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>669.91160000000002</v>
+        <v>659.65279999999996</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>20.795313906332336</v>
+        <v>20.859828352305836</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.7046860936676644</v>
+        <v>-1.6401716476941637</v>
       </c>
       <c r="G13" s="0">
-        <v>1.7046860936676644</v>
+        <v>1.6401716476941637</v>
       </c>
       <c r="H13" s="0">
-        <v>20.295313906332336</v>
+        <v>20.359828352305836</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.2046860936676644</v>
+        <v>-2.1401716476941637</v>
       </c>
       <c r="J13" s="0">
-        <v>2.2046860936676644</v>
+        <v>2.1401716476941637</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1018,28 +1018,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>672.01459999999997</v>
+        <v>682.95950000000005</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>20.956595565307072</v>
+        <v>20.985212682400952</v>
       </c>
       <c r="F14" s="0">
-        <v>0.45659556530707235</v>
+        <v>0.48521268240095239</v>
       </c>
       <c r="G14" s="0">
-        <v>0.45659556530707235</v>
+        <v>0.48521268240095239</v>
       </c>
       <c r="H14" s="0">
-        <v>20.456595565307072</v>
+        <v>20.485212682400952</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.043404434692927652</v>
+        <v>-0.014787317599047611</v>
       </c>
       <c r="J14" s="0">
-        <v>0.043404434692927652</v>
+        <v>0.014787317599047611</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>0</v>
@@ -1062,28 +1062,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>585.0598</v>
+        <v>587.81489999999997</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.770486370542606</v>
+        <v>20.842060523331234</v>
       </c>
       <c r="F15" s="0">
-        <v>1.2704863705426064</v>
+        <v>1.3420605233312344</v>
       </c>
       <c r="G15" s="0">
-        <v>1.2704863705426064</v>
+        <v>1.3420605233312344</v>
       </c>
       <c r="H15" s="0">
-        <v>20.270486370542606</v>
+        <v>20.342060523331234</v>
       </c>
       <c r="I15" s="0">
-        <v>0.77048637054260638</v>
+        <v>0.84206052333123438</v>
       </c>
       <c r="J15" s="0">
-        <v>0.77048637054260638</v>
+        <v>0.84206052333123438</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -1106,28 +1106,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>618.17600000000004</v>
+        <v>624.73410000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.370358004268802</v>
+        <v>21.325133753622261</v>
       </c>
       <c r="F16" s="0">
-        <v>1.8703580042688017</v>
+        <v>1.8251337536222607</v>
       </c>
       <c r="G16" s="0">
-        <v>1.8703580042688017</v>
+        <v>1.8251337536222607</v>
       </c>
       <c r="H16" s="0">
-        <v>20.870358004268802</v>
+        <v>20.825133753622261</v>
       </c>
       <c r="I16" s="0">
-        <v>1.3703580042688017</v>
+        <v>1.3251337536222607</v>
       </c>
       <c r="J16" s="0">
-        <v>1.3703580042688017</v>
+        <v>1.3251337536222607</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1150,28 +1150,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>1122.4987000000001</v>
+        <v>1128.8182999999999</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>20.927554259880168</v>
+        <v>21.004477499402618</v>
       </c>
       <c r="F17" s="0">
-        <v>2.4275542598801678</v>
+        <v>2.5044774994026184</v>
       </c>
       <c r="G17" s="0">
-        <v>2.4275542598801678</v>
+        <v>2.5044774994026184</v>
       </c>
       <c r="H17" s="0">
-        <v>20.427554259880168</v>
+        <v>20.504477499402618</v>
       </c>
       <c r="I17" s="0">
-        <v>1.9275542598801678</v>
+        <v>2.0044774994026184</v>
       </c>
       <c r="J17" s="0">
-        <v>1.9275542598801678</v>
+        <v>2.0044774994026184</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1194,28 +1194,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>1459.4197999999999</v>
+        <v>1473.3333</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>20.794141040813074</v>
+        <v>20.838466000071826</v>
       </c>
       <c r="F18" s="0">
-        <v>-2.9558589591869264</v>
+        <v>-2.9115339999281744</v>
       </c>
       <c r="G18" s="0">
-        <v>2.9558589591869264</v>
+        <v>2.9115339999281744</v>
       </c>
       <c r="H18" s="0">
-        <v>20.294141040813074</v>
+        <v>20.338466000071826</v>
       </c>
       <c r="I18" s="0">
-        <v>-3.4558589591869264</v>
+        <v>-3.4115339999281744</v>
       </c>
       <c r="J18" s="0">
-        <v>3.4558589591869264</v>
+        <v>3.4115339999281744</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1238,28 +1238,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>667.94280000000003</v>
+        <v>676.57719999999995</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.037789675738132</v>
+        <v>20.760904194485139</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.2122103242618678</v>
+        <v>-1.4890958055148609</v>
       </c>
       <c r="G19" s="0">
-        <v>1.2122103242618678</v>
+        <v>1.4890958055148609</v>
       </c>
       <c r="H19" s="0">
-        <v>20.537789675738132</v>
+        <v>20.260904194485139</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.7122103242618678</v>
+        <v>-1.9890958055148609</v>
       </c>
       <c r="J19" s="0">
-        <v>1.7122103242618678</v>
+        <v>1.9890958055148609</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1282,28 +1282,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>755.404</v>
+        <v>752.55830000000003</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>21.003416120735715</v>
+        <v>21.244207373904707</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.4965838792642856</v>
+        <v>-4.2557926260952925</v>
       </c>
       <c r="G20" s="0">
-        <v>4.4965838792642856</v>
+        <v>4.2557926260952925</v>
       </c>
       <c r="H20" s="0">
-        <v>20.503416120735715</v>
+        <v>20.744207373904707</v>
       </c>
       <c r="I20" s="0">
-        <v>-4.9965838792642856</v>
+        <v>-4.7557926260952925</v>
       </c>
       <c r="J20" s="0">
-        <v>4.9965838792642856</v>
+        <v>4.7557926260952925</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1326,28 +1326,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>344.29160000000002</v>
+        <v>349.81529999999998</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>20.807820564163876</v>
+        <v>20.877425435606032</v>
       </c>
       <c r="F21" s="0">
-        <v>-1.692179435836124</v>
+        <v>-1.6225745643939682</v>
       </c>
       <c r="G21" s="0">
-        <v>1.692179435836124</v>
+        <v>1.6225745643939682</v>
       </c>
       <c r="H21" s="0">
-        <v>20.307820564163876</v>
+        <v>20.377425435606032</v>
       </c>
       <c r="I21" s="0">
-        <v>-2.192179435836124</v>
+        <v>-2.1225745643939682</v>
       </c>
       <c r="J21" s="0">
-        <v>2.192179435836124</v>
+        <v>2.1225745643939682</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1370,28 +1370,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>613.17560000000003</v>
+        <v>617.12260000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.965635406716569</v>
+        <v>20.985239959503396</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.53436459328343133</v>
+        <v>-0.51476004049660418</v>
       </c>
       <c r="G22" s="0">
-        <v>0.53436459328343133</v>
+        <v>0.51476004049660418</v>
       </c>
       <c r="H22" s="0">
-        <v>20.465635406716569</v>
+        <v>20.485239959503396</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.0343645932834313</v>
+        <v>-1.0147600404966042</v>
       </c>
       <c r="J22" s="0">
-        <v>1.0343645932834313</v>
+        <v>1.0147600404966042</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1414,28 +1414,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>674.47910000000002</v>
+        <v>669.44370000000004</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.014150079636579</v>
+        <v>21.015023019834889</v>
       </c>
       <c r="F23" s="0">
-        <v>1.014150079636579</v>
+        <v>1.0150230198348886</v>
       </c>
       <c r="G23" s="0">
-        <v>1.014150079636579</v>
+        <v>1.0150230198348886</v>
       </c>
       <c r="H23" s="0">
-        <v>20.514150079636579</v>
+        <v>20.515023019834889</v>
       </c>
       <c r="I23" s="0">
-        <v>0.51415007963657899</v>
+        <v>0.51502301983488863</v>
       </c>
       <c r="J23" s="0">
-        <v>0.51415007963657899</v>
+        <v>0.51502301983488863</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1458,28 +1458,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>577.67240000000004</v>
+        <v>584.04089999999997</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>21.283935803660668</v>
+        <v>21.24204385001902</v>
       </c>
       <c r="F24" s="0">
-        <v>1.7839358036606683</v>
+        <v>1.7420438500190194</v>
       </c>
       <c r="G24" s="0">
-        <v>1.7839358036606683</v>
+        <v>1.7420438500190194</v>
       </c>
       <c r="H24" s="0">
-        <v>20.783935803660668</v>
+        <v>20.74204385001902</v>
       </c>
       <c r="I24" s="0">
-        <v>1.2839358036606683</v>
+        <v>1.2420438500190194</v>
       </c>
       <c r="J24" s="0">
-        <v>1.2839358036606683</v>
+        <v>1.2420438500190194</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>1</v>
@@ -1502,28 +1502,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.55370000000005</v>
+        <v>583.09950000000003</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>21.132170697311839</v>
+        <v>20.940919936957855</v>
       </c>
       <c r="F25" s="0">
-        <v>2.6321706973118388</v>
+        <v>2.4409199369578545</v>
       </c>
       <c r="G25" s="0">
-        <v>2.6321706973118388</v>
+        <v>2.4409199369578545</v>
       </c>
       <c r="H25" s="0">
-        <v>20.632170697311839</v>
+        <v>20.440919936957855</v>
       </c>
       <c r="I25" s="0">
-        <v>2.1321706973118388</v>
+        <v>1.9409199369578545</v>
       </c>
       <c r="J25" s="0">
-        <v>2.1321706973118388</v>
+        <v>1.9409199369578545</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1546,28 +1546,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>688.17229999999995</v>
+        <v>694.29290000000003</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>20.809494739924638</v>
+        <v>20.870062539234621</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.44050526007536206</v>
+        <v>-0.3799374607653796</v>
       </c>
       <c r="G26" s="0">
-        <v>0.44050526007536206</v>
+        <v>0.3799374607653796</v>
       </c>
       <c r="H26" s="0">
-        <v>20.309494739924638</v>
+        <v>20.370062539234621</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.94050526007536206</v>
+        <v>-0.8799374607653796</v>
       </c>
       <c r="J26" s="0">
-        <v>0.94050526007536206</v>
+        <v>0.8799374607653796</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>0</v>
@@ -1590,28 +1590,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>638.71429999999998</v>
+        <v>645.69730000000004</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.988899210687237</v>
+        <v>20.999380730555782</v>
       </c>
       <c r="F27" s="0">
-        <v>1.7388992106872365</v>
+        <v>1.7493807305557816</v>
       </c>
       <c r="G27" s="0">
-        <v>1.7388992106872365</v>
+        <v>1.7493807305557816</v>
       </c>
       <c r="H27" s="0">
-        <v>20.488899210687237</v>
+        <v>20.499380730555782</v>
       </c>
       <c r="I27" s="0">
-        <v>1.2388992106872365</v>
+        <v>1.2493807305557816</v>
       </c>
       <c r="J27" s="0">
-        <v>1.2388992106872365</v>
+        <v>1.2493807305557816</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1634,28 +1634,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>676.74940000000004</v>
+        <v>704.87890000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.003514478580247</v>
+        <v>21.055118417504755</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.74648552141975344</v>
+        <v>-0.69488158249524545</v>
       </c>
       <c r="G28" s="0">
-        <v>0.74648552141975344</v>
+        <v>0.69488158249524545</v>
       </c>
       <c r="H28" s="0">
-        <v>20.503514478580247</v>
+        <v>20.555118417504755</v>
       </c>
       <c r="I28" s="0">
-        <v>-1.2464855214197534</v>
+        <v>-1.1948815824952455</v>
       </c>
       <c r="J28" s="0">
-        <v>1.2464855214197534</v>
+        <v>1.1948815824952455</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1678,28 +1678,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>354.31049999999999</v>
+        <v>353.71350000000001</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>21.001199947408612</v>
+        <v>20.983767113619674</v>
       </c>
       <c r="F29" s="0">
-        <v>0.25119994740861174</v>
+        <v>0.23376711361967395</v>
       </c>
       <c r="G29" s="0">
-        <v>0.25119994740861174</v>
+        <v>0.23376711361967395</v>
       </c>
       <c r="H29" s="0">
-        <v>20.501199947408612</v>
+        <v>20.483767113619674</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.24880005259138827</v>
+        <v>-0.26623288638032605</v>
       </c>
       <c r="J29" s="0">
-        <v>0.24880005259138827</v>
+        <v>0.26623288638032605</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1722,28 +1722,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.81759999999997</v>
+        <v>688.96929999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.175652676042713</v>
+        <v>21.119859986656884</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.32434732395728716</v>
+        <v>-0.38014001334311587</v>
       </c>
       <c r="G30" s="0">
-        <v>0.32434732395728716</v>
+        <v>0.38014001334311587</v>
       </c>
       <c r="H30" s="0">
-        <v>20.675652676042713</v>
+        <v>20.619859986656884</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.82434732395728716</v>
+        <v>-0.88014001334311587</v>
       </c>
       <c r="J30" s="0">
-        <v>0.82434732395728716</v>
+        <v>0.88014001334311587</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1766,28 +1766,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>1353.5838000000001</v>
+        <v>1374.7736</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.444937157780807</v>
+        <v>21.333598598969299</v>
       </c>
       <c r="F31" s="0">
-        <v>1.9449371577808066</v>
+        <v>1.8335985989692993</v>
       </c>
       <c r="G31" s="0">
-        <v>1.9449371577808066</v>
+        <v>1.8335985989692993</v>
       </c>
       <c r="H31" s="0">
-        <v>20.944937157780807</v>
+        <v>20.833598598969299</v>
       </c>
       <c r="I31" s="0">
-        <v>1.4449371577808066</v>
+        <v>1.3335985989692993</v>
       </c>
       <c r="J31" s="0">
-        <v>1.4449371577808066</v>
+        <v>1.3335985989692993</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1810,28 +1810,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>1324.2094</v>
+        <v>1328.4146000000001</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.439782022413272</v>
+        <v>21.329690231635556</v>
       </c>
       <c r="F32" s="0">
-        <v>1.9397820224132723</v>
+        <v>1.8296902316355563</v>
       </c>
       <c r="G32" s="0">
-        <v>1.9397820224132723</v>
+        <v>1.8296902316355563</v>
       </c>
       <c r="H32" s="0">
-        <v>20.939782022413272</v>
+        <v>20.829690231635556</v>
       </c>
       <c r="I32" s="0">
-        <v>1.4397820224132723</v>
+        <v>1.3296902316355563</v>
       </c>
       <c r="J32" s="0">
-        <v>1.4397820224132723</v>
+        <v>1.3296902316355563</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1854,28 +1854,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>1370.5188000000001</v>
+        <v>1401.6427000000001</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>20.9906020780634</v>
+        <v>20.573434580741427</v>
       </c>
       <c r="F33" s="0">
-        <v>-0.009397921936599829</v>
+        <v>-0.42656541925857283</v>
       </c>
       <c r="G33" s="0">
-        <v>0.009397921936599829</v>
+        <v>0.42656541925857283</v>
       </c>
       <c r="H33" s="0">
-        <v>20.4906020780634</v>
+        <v>20.073434580741427</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.50939792193659983</v>
+        <v>-0.92656541925857283</v>
       </c>
       <c r="J33" s="0">
-        <v>0.50939792193659983</v>
+        <v>0.92656541925857283</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>0</v>
@@ -1898,28 +1898,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>595.53899999999999</v>
+        <v>604.36569999999995</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.782357849622571</v>
+        <v>20.851008670781745</v>
       </c>
       <c r="F34" s="0">
-        <v>0.53235784962257071</v>
+        <v>0.60100867078174502</v>
       </c>
       <c r="G34" s="0">
-        <v>0.53235784962257071</v>
+        <v>0.60100867078174502</v>
       </c>
       <c r="H34" s="0">
-        <v>20.282357849622571</v>
+        <v>20.351008670781745</v>
       </c>
       <c r="I34" s="0">
-        <v>0.032357849622570711</v>
+        <v>0.10100867078174502</v>
       </c>
       <c r="J34" s="0">
-        <v>0.032357849622570711</v>
+        <v>0.10100867078174502</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>1</v>
@@ -1942,28 +1942,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>620.18640000000005</v>
+        <v>621.61170000000004</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>21.102616475182231</v>
+        <v>20.87751761035112</v>
       </c>
       <c r="F35" s="0">
-        <v>-0.39738352481776928</v>
+        <v>-0.62248238964888003</v>
       </c>
       <c r="G35" s="0">
-        <v>0.39738352481776928</v>
+        <v>0.62248238964888003</v>
       </c>
       <c r="H35" s="0">
-        <v>20.602616475182231</v>
+        <v>20.37751761035112</v>
       </c>
       <c r="I35" s="0">
-        <v>-0.89738352481776929</v>
+        <v>-1.12248238964888</v>
       </c>
       <c r="J35" s="0">
-        <v>0.89738352481776929</v>
+        <v>1.12248238964888</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1986,28 +1986,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>589.86860000000001</v>
+        <v>597.18910000000005</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>21.102045556971554</v>
+        <v>20.889379616952038</v>
       </c>
       <c r="F36" s="0">
-        <v>1.6020455569715537</v>
+        <v>1.3893796169520378</v>
       </c>
       <c r="G36" s="0">
-        <v>1.6020455569715537</v>
+        <v>1.3893796169520378</v>
       </c>
       <c r="H36" s="0">
-        <v>20.602045556971554</v>
+        <v>20.389379616952038</v>
       </c>
       <c r="I36" s="0">
-        <v>1.1020455569715537</v>
+        <v>0.88937961695203782</v>
       </c>
       <c r="J36" s="0">
-        <v>1.1020455569715537</v>
+        <v>0.88937961695203782</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>1</v>
@@ -2030,28 +2030,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.63610000000006</v>
+        <v>738.8483</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>20.987737542789144</v>
+        <v>21.005555256032352</v>
       </c>
       <c r="F37" s="0">
-        <v>-4.0122624572108556</v>
+        <v>-3.994444743967648</v>
       </c>
       <c r="G37" s="0">
-        <v>4.0122624572108556</v>
+        <v>3.994444743967648</v>
       </c>
       <c r="H37" s="0">
-        <v>20.487737542789144</v>
+        <v>20.505555256032352</v>
       </c>
       <c r="I37" s="0">
-        <v>-4.5122624572108556</v>
+        <v>-4.494444743967648</v>
       </c>
       <c r="J37" s="0">
-        <v>4.5122624572108556</v>
+        <v>4.494444743967648</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2074,28 +2074,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>598.2287</v>
+        <v>595.78989999999999</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>21.003521492488353</v>
+        <v>21.020410665595897</v>
       </c>
       <c r="F38" s="0">
-        <v>2.0035214924883533</v>
+        <v>2.0204106655958967</v>
       </c>
       <c r="G38" s="0">
-        <v>2.0035214924883533</v>
+        <v>2.0204106655958967</v>
       </c>
       <c r="H38" s="0">
-        <v>20.503521492488353</v>
+        <v>20.520410665595897</v>
       </c>
       <c r="I38" s="0">
-        <v>1.5035214924883533</v>
+        <v>1.5204106655958967</v>
       </c>
       <c r="J38" s="0">
-        <v>1.5035214924883533</v>
+        <v>1.5204106655958967</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2118,28 +2118,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>681.9153</v>
+        <v>698.92719999999997</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.773573810543194</v>
+        <v>20.841705640473208</v>
       </c>
       <c r="F39" s="0">
-        <v>1.7735738105431942</v>
+        <v>1.841705640473208</v>
       </c>
       <c r="G39" s="0">
-        <v>1.7735738105431942</v>
+        <v>1.841705640473208</v>
       </c>
       <c r="H39" s="0">
-        <v>20.273573810543194</v>
+        <v>20.341705640473208</v>
       </c>
       <c r="I39" s="0">
-        <v>1.2735738105431942</v>
+        <v>1.341705640473208</v>
       </c>
       <c r="J39" s="0">
-        <v>1.2735738105431942</v>
+        <v>1.341705640473208</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2162,28 +2162,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>1171.8478</v>
+        <v>1170.2615000000001</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>21.080122903846071</v>
+        <v>20.973178740081771</v>
       </c>
       <c r="F40" s="0">
-        <v>0.080122903846071125</v>
+        <v>-0.026821259918229146</v>
       </c>
       <c r="G40" s="0">
-        <v>0.080122903846071125</v>
+        <v>0.026821259918229146</v>
       </c>
       <c r="H40" s="0">
-        <v>20.580122903846071</v>
+        <v>20.473178740081771</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.41987709615392888</v>
+        <v>-0.52682125991822915</v>
       </c>
       <c r="J40" s="0">
-        <v>0.41987709615392888</v>
+        <v>0.52682125991822915</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>0</v>
@@ -2206,28 +2206,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>665.75360000000001</v>
+        <v>672.51900000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.101100837816599</v>
+        <v>21.044053999128213</v>
       </c>
       <c r="F41" s="0">
-        <v>0.60110083781659895</v>
+        <v>0.54405399912821295</v>
       </c>
       <c r="G41" s="0">
-        <v>0.60110083781659895</v>
+        <v>0.54405399912821295</v>
       </c>
       <c r="H41" s="0">
-        <v>20.601100837816599</v>
+        <v>20.544053999128213</v>
       </c>
       <c r="I41" s="0">
-        <v>0.10110083781659895</v>
+        <v>0.044053999128212951</v>
       </c>
       <c r="J41" s="0">
-        <v>0.10110083781659895</v>
+        <v>0.044053999128212951</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2250,28 +2250,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>343.99220000000003</v>
+        <v>344.02600000000001</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>21.040191709581929</v>
+        <v>21.003343237027668</v>
       </c>
       <c r="F42" s="0">
-        <v>1.7901917095819293</v>
+        <v>1.7533432370276678</v>
       </c>
       <c r="G42" s="0">
-        <v>1.7901917095819293</v>
+        <v>1.7533432370276678</v>
       </c>
       <c r="H42" s="0">
-        <v>20.540191709581929</v>
+        <v>20.503343237027668</v>
       </c>
       <c r="I42" s="0">
-        <v>1.2901917095819293</v>
+        <v>1.2533432370276678</v>
       </c>
       <c r="J42" s="0">
-        <v>1.2901917095819293</v>
+        <v>1.2533432370276678</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>1</v>
@@ -2294,28 +2294,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>584.32039999999995</v>
+        <v>585.99260000000004</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>21.003624449799588</v>
+        <v>20.838155877320844</v>
       </c>
       <c r="F43" s="0">
-        <v>1.0036244497995881</v>
+        <v>0.83815587732084396</v>
       </c>
       <c r="G43" s="0">
-        <v>1.0036244497995881</v>
+        <v>0.83815587732084396</v>
       </c>
       <c r="H43" s="0">
-        <v>20.503624449799588</v>
+        <v>20.338155877320844</v>
       </c>
       <c r="I43" s="0">
-        <v>0.50362444979958809</v>
+        <v>0.33815587732084396</v>
       </c>
       <c r="J43" s="0">
-        <v>0.50362444979958809</v>
+        <v>0.33815587732084396</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>1</v>
@@ -2338,28 +2338,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>660.15719999999999</v>
+        <v>661.50829999999996</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>20.78660828283418</v>
+        <v>20.852926596443769</v>
       </c>
       <c r="F44" s="0">
-        <v>0.78660828283418027</v>
+        <v>0.85292659644376911</v>
       </c>
       <c r="G44" s="0">
-        <v>0.78660828283418027</v>
+        <v>0.85292659644376911</v>
       </c>
       <c r="H44" s="0">
-        <v>20.28660828283418</v>
+        <v>20.352926596443769</v>
       </c>
       <c r="I44" s="0">
-        <v>0.28660828283418027</v>
+        <v>0.35292659644376911</v>
       </c>
       <c r="J44" s="0">
-        <v>0.28660828283418027</v>
+        <v>0.35292659644376911</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2382,28 +2382,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>581.95590000000004</v>
+        <v>579.78219999999999</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>21.117078755193056</v>
+        <v>20.920199185383829</v>
       </c>
       <c r="F45" s="0">
-        <v>1.1170787551930559</v>
+        <v>0.92019918538382939</v>
       </c>
       <c r="G45" s="0">
-        <v>1.1170787551930559</v>
+        <v>0.92019918538382939</v>
       </c>
       <c r="H45" s="0">
-        <v>20.617078755193056</v>
+        <v>20.420199185383829</v>
       </c>
       <c r="I45" s="0">
-        <v>0.61707875519305588</v>
+        <v>0.42019918538382939</v>
       </c>
       <c r="J45" s="0">
-        <v>0.61707875519305588</v>
+        <v>0.42019918538382939</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>1</v>
@@ -2426,28 +2426,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>1432.1427000000001</v>
+        <v>1450.9502</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>20.810571632932547</v>
+        <v>20.851828252803998</v>
       </c>
       <c r="F46" s="0">
-        <v>-1.1894283670674533</v>
+        <v>-1.1481717471960025</v>
       </c>
       <c r="G46" s="0">
-        <v>1.1894283670674533</v>
+        <v>1.1481717471960025</v>
       </c>
       <c r="H46" s="0">
-        <v>20.310571632932547</v>
+        <v>20.351828252803998</v>
       </c>
       <c r="I46" s="0">
-        <v>-1.6894283670674533</v>
+        <v>-1.6481717471960025</v>
       </c>
       <c r="J46" s="0">
-        <v>1.6894283670674533</v>
+        <v>1.6481717471960025</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2470,28 +2470,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>1393.6792</v>
+        <v>1401.4597000000001</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>20.810629094658204</v>
+        <v>20.85313038766477</v>
       </c>
       <c r="F47" s="0">
-        <v>-1.1893709053417965</v>
+        <v>-1.1468696123352302</v>
       </c>
       <c r="G47" s="0">
-        <v>1.1893709053417965</v>
+        <v>1.1468696123352302</v>
       </c>
       <c r="H47" s="0">
-        <v>20.310629094658204</v>
+        <v>20.35313038766477</v>
       </c>
       <c r="I47" s="0">
-        <v>-1.6893709053417965</v>
+        <v>-1.6468696123352302</v>
       </c>
       <c r="J47" s="0">
-        <v>1.6893709053417965</v>
+        <v>1.6468696123352302</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2514,28 +2514,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>1418.9514999999999</v>
+        <v>1394.8155999999999</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.12777341289566</v>
+        <v>20.729069030825691</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.8722265871043398</v>
+        <v>-2.2709309691743087</v>
       </c>
       <c r="G48" s="0">
-        <v>1.8722265871043398</v>
+        <v>2.2709309691743087</v>
       </c>
       <c r="H48" s="0">
-        <v>20.62777341289566</v>
+        <v>20.229069030825691</v>
       </c>
       <c r="I48" s="0">
-        <v>-2.3722265871043398</v>
+        <v>-2.7709309691743087</v>
       </c>
       <c r="J48" s="0">
-        <v>2.3722265871043398</v>
+        <v>2.7709309691743087</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2558,28 +2558,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>1319.8444999999999</v>
+        <v>1329.1301000000001</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>21.075305398992192</v>
+        <v>20.665020408339853</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.67469460100780765</v>
+        <v>-1.0849795916601472</v>
       </c>
       <c r="G49" s="0">
-        <v>0.67469460100780765</v>
+        <v>1.0849795916601472</v>
       </c>
       <c r="H49" s="0">
-        <v>20.575305398992192</v>
+        <v>20.165020408339853</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.1746946010078077</v>
+        <v>-1.5849795916601472</v>
       </c>
       <c r="J49" s="0">
-        <v>1.1746946010078077</v>
+        <v>1.5849795916601472</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2602,28 +2602,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>1370.9471000000001</v>
+        <v>1378.3186000000001</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.00342689770892</v>
+        <v>21.351297107080605</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.4965731022910802</v>
+        <v>-0.14870289291939542</v>
       </c>
       <c r="G50" s="0">
-        <v>0.4965731022910802</v>
+        <v>0.14870289291939542</v>
       </c>
       <c r="H50" s="0">
-        <v>20.50342689770892</v>
+        <v>20.851297107080605</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.9965731022910802</v>
+        <v>-0.64870289291939543</v>
       </c>
       <c r="J50" s="0">
-        <v>0.9965731022910802</v>
+        <v>0.64870289291939543</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2646,28 +2646,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>1230.9086</v>
+        <v>1221.2897</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>21.289007247266369</v>
+        <v>21.183246262427531</v>
       </c>
       <c r="F51" s="0">
-        <v>2.0890072472663697</v>
+        <v>1.9832462624275315</v>
       </c>
       <c r="G51" s="0">
-        <v>2.0890072472663697</v>
+        <v>1.9832462624275315</v>
       </c>
       <c r="H51" s="0">
-        <v>20.789007247266369</v>
+        <v>20.683246262427531</v>
       </c>
       <c r="I51" s="0">
-        <v>1.5890072472663697</v>
+        <v>1.4832462624275315</v>
       </c>
       <c r="J51" s="0">
-        <v>1.5890072472663697</v>
+        <v>1.4832462624275315</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2690,28 +2690,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>1142.3658</v>
+        <v>1153.4326000000001</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>21.071965201198314</v>
+        <v>20.669837535648107</v>
       </c>
       <c r="F52" s="0">
-        <v>3.5719652011983136</v>
+        <v>3.1698375356481066</v>
       </c>
       <c r="G52" s="0">
-        <v>3.5719652011983136</v>
+        <v>3.1698375356481066</v>
       </c>
       <c r="H52" s="0">
-        <v>20.571965201198314</v>
+        <v>20.169837535648107</v>
       </c>
       <c r="I52" s="0">
-        <v>3.0719652011983136</v>
+        <v>2.6698375356481066</v>
       </c>
       <c r="J52" s="0">
-        <v>3.0719652011983136</v>
+        <v>2.6698375356481066</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2734,28 +2734,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>1183.6578999999999</v>
+        <v>1196.1094000000001</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>20.931955269114045</v>
+        <v>21.011628539638849</v>
       </c>
       <c r="F53" s="0">
-        <v>2.5319552691140466</v>
+        <v>2.6116285396388506</v>
       </c>
       <c r="G53" s="0">
-        <v>2.5319552691140466</v>
+        <v>2.6116285396388506</v>
       </c>
       <c r="H53" s="0">
-        <v>20.431955269114045</v>
+        <v>20.511628539638849</v>
       </c>
       <c r="I53" s="0">
-        <v>2.0319552691140466</v>
+        <v>2.1116285396388506</v>
       </c>
       <c r="J53" s="0">
-        <v>2.0319552691140466</v>
+        <v>2.1116285396388506</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2778,28 +2778,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>1127.7965999999999</v>
+        <v>1146.1387</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>21.003458715916942</v>
+        <v>21.241685143987279</v>
       </c>
       <c r="F54" s="0">
-        <v>2.0034587159169419</v>
+        <v>2.2416851439872794</v>
       </c>
       <c r="G54" s="0">
-        <v>2.0034587159169419</v>
+        <v>2.2416851439872794</v>
       </c>
       <c r="H54" s="0">
-        <v>20.503458715916942</v>
+        <v>20.741685143987279</v>
       </c>
       <c r="I54" s="0">
-        <v>1.5034587159169419</v>
+        <v>1.7416851439872794</v>
       </c>
       <c r="J54" s="0">
-        <v>1.5034587159169419</v>
+        <v>1.7416851439872794</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2822,28 +2822,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.21460000000002</v>
+        <v>610.65390000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>21.003449475248658</v>
+        <v>21.158709672502599</v>
       </c>
       <c r="F55" s="0">
-        <v>1.503449475248658</v>
+        <v>1.6587096725025994</v>
       </c>
       <c r="G55" s="0">
-        <v>1.503449475248658</v>
+        <v>1.6587096725025994</v>
       </c>
       <c r="H55" s="0">
-        <v>20.503449475248658</v>
+        <v>20.658709672502599</v>
       </c>
       <c r="I55" s="0">
-        <v>1.003449475248658</v>
+        <v>1.1587096725025994</v>
       </c>
       <c r="J55" s="0">
-        <v>1.003449475248658</v>
+        <v>1.1587096725025994</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2866,28 +2866,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>684.51480000000004</v>
+        <v>701.03470000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>20.826953127794582</v>
+        <v>20.883572835929062</v>
       </c>
       <c r="F56" s="0">
-        <v>0.32695312779458163</v>
+        <v>0.383572835929062</v>
       </c>
       <c r="G56" s="0">
-        <v>0.32695312779458163</v>
+        <v>0.383572835929062</v>
       </c>
       <c r="H56" s="0">
-        <v>20.326953127794582</v>
+        <v>20.383572835929062</v>
       </c>
       <c r="I56" s="0">
-        <v>-0.17304687220541837</v>
+        <v>-0.11642716407093801</v>
       </c>
       <c r="J56" s="0">
-        <v>0.17304687220541837</v>
+        <v>0.11642716407093801</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>0</v>
@@ -2910,28 +2910,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>632.78740000000005</v>
+        <v>647.98350000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>21.032088122911066</v>
+        <v>20.766738729372591</v>
       </c>
       <c r="F57" s="0">
-        <v>0.032088122911066108</v>
+        <v>-0.23326127062740909</v>
       </c>
       <c r="G57" s="0">
-        <v>0.032088122911066108</v>
+        <v>0.23326127062740909</v>
       </c>
       <c r="H57" s="0">
-        <v>20.532088122911066</v>
+        <v>20.266738729372591</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.46791187708893389</v>
+        <v>-0.73326127062740909</v>
       </c>
       <c r="J57" s="0">
-        <v>0.46791187708893389</v>
+        <v>0.73326127062740909</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2954,28 +2954,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>1105.7334000000001</v>
+        <v>1095.0534</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>20.930757399296425</v>
+        <v>21.004471137556791</v>
       </c>
       <c r="F58" s="0">
-        <v>-2.5692426007035749</v>
+        <v>-2.4955288624432086</v>
       </c>
       <c r="G58" s="0">
-        <v>2.5692426007035749</v>
+        <v>2.4955288624432086</v>
       </c>
       <c r="H58" s="0">
-        <v>20.430757399296425</v>
+        <v>20.504471137556791</v>
       </c>
       <c r="I58" s="0">
-        <v>-3.0692426007035749</v>
+        <v>-2.9955288624432086</v>
       </c>
       <c r="J58" s="0">
-        <v>3.0692426007035749</v>
+        <v>2.9955288624432086</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2998,31 +2998,31 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.27829999999995</v>
+        <v>672.01580000000001</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.045846146554705</v>
+        <v>20.986757063275959</v>
       </c>
       <c r="F59" s="0">
-        <v>0.54584614655470531</v>
+        <v>0.48675706327595947</v>
       </c>
       <c r="G59" s="0">
-        <v>0.54584614655470531</v>
+        <v>0.48675706327595947</v>
       </c>
       <c r="H59" s="0">
-        <v>20.545846146554705</v>
+        <v>20.486757063275959</v>
       </c>
       <c r="I59" s="0">
-        <v>0.045846146554705314</v>
+        <v>-0.013242936724040533</v>
       </c>
       <c r="J59" s="0">
-        <v>0.045846146554705314</v>
+        <v>0.013242936724040533</v>
       </c>
       <c r="K59" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="0">
         <v>2</v>
@@ -3042,28 +3042,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>655.14710000000002</v>
+        <v>697.428</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.003579286366666</v>
+        <v>20.937203217954192</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.49642071363333429</v>
+        <v>-0.56279678204580819</v>
       </c>
       <c r="G60" s="0">
-        <v>0.49642071363333429</v>
+        <v>0.56279678204580819</v>
       </c>
       <c r="H60" s="0">
-        <v>20.503579286366666</v>
+        <v>20.437203217954192</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.99642071363333429</v>
+        <v>-1.0627967820458082</v>
       </c>
       <c r="J60" s="0">
-        <v>0.99642071363333429</v>
+        <v>1.0627967820458082</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3086,28 +3086,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>642.19590000000005</v>
+        <v>648.5258</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.959634958298267</v>
+        <v>20.984400241916585</v>
       </c>
       <c r="F61" s="0">
-        <v>0.95963495829826684</v>
+        <v>0.98440024191658537</v>
       </c>
       <c r="G61" s="0">
-        <v>0.95963495829826684</v>
+        <v>0.98440024191658537</v>
       </c>
       <c r="H61" s="0">
-        <v>20.459634958298267</v>
+        <v>20.484400241916585</v>
       </c>
       <c r="I61" s="0">
-        <v>0.45963495829826684</v>
+        <v>0.48440024191658537</v>
       </c>
       <c r="J61" s="0">
-        <v>0.45963495829826684</v>
+        <v>0.48440024191658537</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3130,28 +3130,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>671.02829999999995</v>
+        <v>690.99220000000003</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>20.962775383513446</v>
+        <v>20.988565945106131</v>
       </c>
       <c r="F62" s="0">
-        <v>-2.0372246164865544</v>
+        <v>-2.0114340548938685</v>
       </c>
       <c r="G62" s="0">
-        <v>2.0372246164865544</v>
+        <v>2.0114340548938685</v>
       </c>
       <c r="H62" s="0">
-        <v>20.462775383513446</v>
+        <v>20.488565945106131</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.5372246164865544</v>
+        <v>-2.5114340548938685</v>
       </c>
       <c r="J62" s="0">
-        <v>2.5372246164865544</v>
+        <v>2.5114340548938685</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3174,28 +3174,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>658.74609999999996</v>
+        <v>674.3954</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>20.785522729548532</v>
+        <v>20.851731983499494</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.71447727045146792</v>
+        <v>-0.6482680165005057</v>
       </c>
       <c r="G63" s="0">
-        <v>0.71447727045146792</v>
+        <v>0.6482680165005057</v>
       </c>
       <c r="H63" s="0">
-        <v>20.285522729548532</v>
+        <v>20.351731983499494</v>
       </c>
       <c r="I63" s="0">
-        <v>-1.2144772704514679</v>
+        <v>-1.1482680165005057</v>
       </c>
       <c r="J63" s="0">
-        <v>1.2144772704514679</v>
+        <v>1.1482680165005057</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3218,28 +3218,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>418.81540000000001</v>
+        <v>427.42320000000001</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>21.003509091462448</v>
+        <v>21.02590665422743</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.4964909085375524</v>
+        <v>-1.4740933457725696</v>
       </c>
       <c r="G64" s="0">
-        <v>1.4964909085375524</v>
+        <v>1.4740933457725696</v>
       </c>
       <c r="H64" s="0">
-        <v>20.503509091462448</v>
+        <v>20.52590665422743</v>
       </c>
       <c r="I64" s="0">
-        <v>-1.9964909085375524</v>
+        <v>-1.9740933457725696</v>
       </c>
       <c r="J64" s="0">
-        <v>1.9964909085375524</v>
+        <v>1.9740933457725696</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3262,28 +3262,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>593.42259999999999</v>
+        <v>597.84789999999998</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>20.893790247983933</v>
+        <v>20.839128594375872</v>
       </c>
       <c r="F65" s="0">
-        <v>1.643790247983933</v>
+        <v>1.5891285943758717</v>
       </c>
       <c r="G65" s="0">
-        <v>1.643790247983933</v>
+        <v>1.5891285943758717</v>
       </c>
       <c r="H65" s="0">
-        <v>20.393790247983933</v>
+        <v>20.339128594375872</v>
       </c>
       <c r="I65" s="0">
-        <v>1.143790247983933</v>
+        <v>1.0891285943758717</v>
       </c>
       <c r="J65" s="0">
-        <v>1.143790247983933</v>
+        <v>1.0891285943758717</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3306,28 +3306,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>709.44029999999998</v>
+        <v>710.17049999999995</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.068876605698904</v>
+        <v>20.787805348868485</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.4311233943010961</v>
+        <v>-2.7121946511315152</v>
       </c>
       <c r="G66" s="0">
-        <v>2.4311233943010961</v>
+        <v>2.7121946511315152</v>
       </c>
       <c r="H66" s="0">
-        <v>20.568876605698904</v>
+        <v>20.287805348868485</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.9311233943010962</v>
+        <v>-3.2121946511315151</v>
       </c>
       <c r="J66" s="0">
-        <v>2.9311233943010962</v>
+        <v>3.2121946511315151</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3350,28 +3350,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>625.83199999999999</v>
+        <v>639.05380000000002</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>21.067303670408336</v>
+        <v>20.819042766917708</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.43269632959166415</v>
+        <v>-0.68095723308229239</v>
       </c>
       <c r="G67" s="0">
-        <v>0.43269632959166415</v>
+        <v>0.68095723308229239</v>
       </c>
       <c r="H67" s="0">
-        <v>20.567303670408336</v>
+        <v>20.319042766917708</v>
       </c>
       <c r="I67" s="0">
-        <v>-0.93269632959166415</v>
+        <v>-1.1809572330822924</v>
       </c>
       <c r="J67" s="0">
-        <v>0.93269632959166415</v>
+        <v>1.1809572330822924</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3394,28 +3394,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>889.9828</v>
+        <v>892.07839999999999</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>21.067216412761553</v>
+        <v>20.717317441501862</v>
       </c>
       <c r="F68" s="0">
-        <v>2.0672164127615531</v>
+        <v>1.7173174415018622</v>
       </c>
       <c r="G68" s="0">
-        <v>2.0672164127615531</v>
+        <v>1.7173174415018622</v>
       </c>
       <c r="H68" s="0">
-        <v>20.567216412761553</v>
+        <v>20.217317441501862</v>
       </c>
       <c r="I68" s="0">
-        <v>1.5672164127615531</v>
+        <v>1.2173174415018622</v>
       </c>
       <c r="J68" s="0">
-        <v>1.5672164127615531</v>
+        <v>1.2173174415018622</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3476,16 +3476,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.4590000000000001</v>
+        <v>1.458</v>
       </c>
       <c r="C2" s="0">
-        <v>1.811</v>
+        <v>1.8080000000000001</v>
       </c>
       <c r="D2" s="0">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="E2" s="0">
-        <v>0.021000000000000001</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3495,22 +3495,22 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0.0070000000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0080000000000000002</v>
+        <v>0.014</v>
       </c>
       <c r="D3" s="0">
-        <v>0.012999999999999999</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="E3" s="0">
-        <v>0.042999999999999997</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="F3" s="0">
-        <v>2.3999999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="G3" s="0">
-        <v>2</v>
+        <v>2.7000000000000002</v>
       </c>
     </row>
     <row r="4">
@@ -3529,18 +3529,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.478</v>
+        <v>1.4730000000000001</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.47899999999999998</v>
+        <v>-0.47099999999999998</v>
       </c>
       <c r="F5" s="0">
-        <v>38.200000000000003</v>
+        <v>38.399999999999999</v>
       </c>
       <c r="G5" s="0">
-        <v>42.799999999999997</v>
+        <v>43.100000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -3567,7 +3567,7 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.51</v>
+        <v>1.5089999999999999</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
@@ -3663,7 +3663,7 @@
     <col min="2" max="2" width="7.7109375" customWidth="true"/>
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
     <col min="4" max="4" width="6.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="5" max="5" width="5.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3688,13 +3688,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>21.556100000000001</v>
+        <v>21.5443</v>
       </c>
       <c r="C2" s="0">
-        <v>0.80569999999999997</v>
+        <v>0.80659999999999998</v>
       </c>
       <c r="D2" s="0">
-        <v>26.753</v>
+        <v>26.710999999999999</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3711,10 +3711,10 @@
         <v>0.00069999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>0.40000000000000002</v>
+        <v>0.41999999999999999</v>
       </c>
       <c r="E3" s="0">
-        <v>0.69079999999999997</v>
+        <v>0.67600000000000005</v>
       </c>
     </row>
     <row r="4">
@@ -3728,10 +3728,10 @@
         <v>0.0132</v>
       </c>
       <c r="D4" s="0">
-        <v>-1.4490000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="E4" s="0">
-        <v>0.15210000000000001</v>
+        <v>0.15179999999999999</v>
       </c>
     </row>
   </sheetData>
